--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46227.63541666666</v>
+        <v>46227.625</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46227.64583333334</v>
+        <v>46227.63541666666</v>
       </c>
     </row>
     <row r="19">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46227.65625</v>
+        <v>46227.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46227.66666666666</v>
+        <v>46227.65625</v>
       </c>
     </row>
     <row r="25">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46227.70833333334</v>
+        <v>46227.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46227.79166666666</v>
+        <v>46227.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="AU29" s="3" t="n">
-        <v>46227.83333333334</v>
+        <v>46227.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -5130,27 +5130,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.83333333334</v>
       </c>
     </row>
     <row r="31">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU56"/>
+  <dimension ref="A1:AU55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.89583333334</v>
       </c>
     </row>
     <row r="53">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46227.95833333334</v>
       </c>
     </row>
     <row r="55">
@@ -9255,165 +9255,6 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46227.95833333334</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" s="3" t="n">
         <v>46227.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU55"/>
+  <dimension ref="A1:AU54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8469,27 +8469,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.89583333334</v>
       </c>
     </row>
     <row r="52">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46227.95833333334</v>
       </c>
     </row>
     <row r="54">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9096,165 +9096,6 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46227.95833333334</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" s="3" t="n">
         <v>46227.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>4.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.08</v>
+        <v>1.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>4.92</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>4.92</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>3.08</v>
       </c>
       <c r="O23" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>4.92</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU54"/>
+  <dimension ref="A1:AU51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>3.08</v>
       </c>
       <c r="O22" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>4.92</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7992,27 +7992,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.89583333334</v>
       </c>
     </row>
     <row r="49">
@@ -8151,27 +8151,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.89583333334</v>
       </c>
     </row>
     <row r="50">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.95833333334</v>
       </c>
     </row>
     <row r="51">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8619,483 +8619,6 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46227.89583333334</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Colo-Colo</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" s="3" t="n">
-        <v>46227.89583333334</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" s="3" t="n">
-        <v>46227.95833333334</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" s="3" t="n">
         <v>46227.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.08</v>
+        <v>1.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>4.92</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.08</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>4.92</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>3.08</v>
       </c>
       <c r="O23" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>4.92</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O22" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="O34" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>6.65</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="P16" t="n">
-        <v>5.81</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.78</v>
+        <v>1.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>4.92</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>3.08</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>4.92</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>4.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>5.81</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>4.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O23" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G43" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.34</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="U4" t="n">
-        <v>2.96</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P16" t="n">
-        <v>4.94</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P37" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>5.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O23" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.08</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>4.92</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU51"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.34</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="U4" t="n">
-        <v>2.96</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3278,55 +3278,55 @@
         <v>5.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3437,34 +3437,34 @@
         <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.85</v>
@@ -3473,19 +3473,19 @@
         <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3596,55 +3596,55 @@
         <v>3.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>4.92</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6458,55 +6458,55 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7833,27 +7833,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.89583333334</v>
       </c>
     </row>
     <row r="48">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>46227.89583333334</v>
+        <v>46227.95833333334</v>
       </c>
     </row>
     <row r="50">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8460,165 +8460,6 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46227.95833333334</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" s="3" t="n">
         <v>46227.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>5.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
         <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.71</v>
+        <v>2.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="P16" t="n">
-        <v>5.81</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
         <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U19" t="n">
         <v>3.4</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.56</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.04</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.75</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.27</v>
-      </c>
       <c r="U20" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3755,34 +3755,34 @@
         <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
         <v>1.75</v>
@@ -3791,19 +3791,19 @@
         <v>1.94</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U24" t="n">
         <v>2.78</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4391,55 +4391,55 @@
         <v>4.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -4721,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4739,25 +4739,25 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5345,55 +5345,55 @@
         <v>6.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5663,55 +5663,55 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6458,55 +6458,55 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O44" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G50" t="n">

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU50"/>
+  <dimension ref="A1:AU44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.39</v>
+        <v>1.99</v>
       </c>
       <c r="S14" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>2.21</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.16</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.48</v>
+        <v>3.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="R15" t="n">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="S15" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="U15" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.03</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.21</v>
+        <v>1.58</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.94</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P19" t="n">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.75</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.27</v>
-      </c>
       <c r="U19" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U20" t="n">
         <v>3.4</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.56</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.04</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>4.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O23" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S24" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="U24" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46227.83333333334</v>
+        <v>46227.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,68 +5332,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.83333333334</v>
       </c>
     </row>
     <row r="32">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5663,55 +5663,55 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6617,55 +6617,55 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6879,27 +6879,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.89583333334</v>
       </c>
     </row>
     <row r="42">
@@ -7038,27 +7038,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="AU42" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.89583333334</v>
       </c>
     </row>
     <row r="43">
@@ -7197,27 +7197,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46227.875</v>
+        <v>46227.95833333334</v>
       </c>
     </row>
     <row r="44">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7506,960 +7506,6 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46227.875</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Mačva Šabac</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Partizan</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" s="3" t="n">
-        <v>46227.875</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Red Star Belgrade</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Vojvodina</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" s="3" t="n">
-        <v>46227.875</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" s="3" t="n">
-        <v>46227.89583333334</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Colo-Colo</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="O48" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P48" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" s="3" t="n">
-        <v>46227.89583333334</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" s="3" t="n">
-        <v>46227.95833333334</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" s="3" t="n">
         <v>46227.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>2.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>3.72</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="T4" t="n">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3.72</v>
       </c>
       <c r="R3" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="S3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.2</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.72</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.05</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="O10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.4</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>4.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.94</v>
+        <v>5.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="S14" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.03</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.21</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.94</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>2.39</v>
+        <v>1.99</v>
       </c>
       <c r="S15" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.58</v>
+        <v>2.21</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.16</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.48</v>
+        <v>3.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O22" t="n">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O23" t="n">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6458,55 +6458,55 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.35</v>
+        <v>3.12</v>
       </c>
       <c r="R39" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T39" t="n">
-        <v>4.4</v>
+        <v>2.31</v>
       </c>
       <c r="U39" t="n">
-        <v>1.99</v>
+        <v>2.67</v>
       </c>
       <c r="V39" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.75</v>
+        <v>3.42</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.93</v>
+        <v>3.08</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.57</v>
+        <v>2.03</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="P40" t="n">
-        <v>2.75</v>
+        <v>6.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="R40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC40" t="n">
         <v>2.25</v>
       </c>
-      <c r="S40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU55"/>
+  <dimension ref="A1:AU44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3">
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1296,34 +1296,34 @@
         <v>4.47</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
         <v>1.72</v>
@@ -1332,19 +1332,19 @@
         <v>2.07</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>5.81</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>4.94</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3415,34 +3415,34 @@
         <v>2.42</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
         <v>1.85</v>
@@ -3451,19 +3451,19 @@
         <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>3.07</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="O21">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="P21">
-        <v>2.48</v>
+        <v>4.92</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB21">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>2.24</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O23">
-        <v>3.64</v>
+        <v>3.14</v>
       </c>
       <c r="P23">
-        <v>4.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA23">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AB23">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>2.03</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA24">
         <v>1.75</v>
@@ -4266,19 +4266,19 @@
         <v>1.94</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>4.83</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -4731,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -4749,25 +4749,25 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>2.75</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G33">
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G40">
@@ -6825,68 +6825,68 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 23:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G44">
@@ -7584,1799 +7584,6 @@
         <v>0</v>
       </c>
       <c r="AU44" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>FYR Macedonia First Football League</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Tikveš</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Aresimi</t>
-        </is>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>0</v>
-      </c>
-      <c r="Y45">
-        <v>0</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45">
-        <v>0</v>
-      </c>
-      <c r="AB45">
-        <v>0</v>
-      </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AD45">
-        <v>0</v>
-      </c>
-      <c r="AE45">
-        <v>0</v>
-      </c>
-      <c r="AF45">
-        <v>0</v>
-      </c>
-      <c r="AG45">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>0</v>
-      </c>
-      <c r="AK45">
-        <v>0</v>
-      </c>
-      <c r="AL45">
-        <v>0</v>
-      </c>
-      <c r="AM45">
-        <v>-1</v>
-      </c>
-      <c r="AN45">
-        <v>-1</v>
-      </c>
-      <c r="AO45">
-        <v>-1</v>
-      </c>
-      <c r="AP45">
-        <v>-1</v>
-      </c>
-      <c r="AQ45">
-        <v>0</v>
-      </c>
-      <c r="AR45">
-        <v>0</v>
-      </c>
-      <c r="AS45">
-        <v>0</v>
-      </c>
-      <c r="AT45">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Hungary NB I</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Debrecen</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Puskás</t>
-        </is>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46">
-        <v>0</v>
-      </c>
-      <c r="Y46">
-        <v>0</v>
-      </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-      <c r="AA46">
-        <v>0</v>
-      </c>
-      <c r="AB46">
-        <v>0</v>
-      </c>
-      <c r="AC46">
-        <v>0</v>
-      </c>
-      <c r="AD46">
-        <v>0</v>
-      </c>
-      <c r="AE46">
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <v>0</v>
-      </c>
-      <c r="AG46">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>0</v>
-      </c>
-      <c r="AK46">
-        <v>0</v>
-      </c>
-      <c r="AL46">
-        <v>0</v>
-      </c>
-      <c r="AM46">
-        <v>-1</v>
-      </c>
-      <c r="AN46">
-        <v>-1</v>
-      </c>
-      <c r="AO46">
-        <v>-1</v>
-      </c>
-      <c r="AP46">
-        <v>-1</v>
-      </c>
-      <c r="AQ46">
-        <v>0</v>
-      </c>
-      <c r="AR46">
-        <v>0</v>
-      </c>
-      <c r="AS46">
-        <v>0</v>
-      </c>
-      <c r="AT46">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Hungary NB I</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>MTK</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Zalaegerszegi TE</t>
-        </is>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>0</v>
-      </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-      <c r="AA47">
-        <v>0</v>
-      </c>
-      <c r="AB47">
-        <v>0</v>
-      </c>
-      <c r="AC47">
-        <v>0</v>
-      </c>
-      <c r="AD47">
-        <v>0</v>
-      </c>
-      <c r="AE47">
-        <v>0</v>
-      </c>
-      <c r="AF47">
-        <v>0</v>
-      </c>
-      <c r="AG47">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>0</v>
-      </c>
-      <c r="AK47">
-        <v>0</v>
-      </c>
-      <c r="AL47">
-        <v>0</v>
-      </c>
-      <c r="AM47">
-        <v>-1</v>
-      </c>
-      <c r="AN47">
-        <v>-1</v>
-      </c>
-      <c r="AO47">
-        <v>-1</v>
-      </c>
-      <c r="AP47">
-        <v>-1</v>
-      </c>
-      <c r="AQ47">
-        <v>0</v>
-      </c>
-      <c r="AR47">
-        <v>0</v>
-      </c>
-      <c r="AS47">
-        <v>0</v>
-      </c>
-      <c r="AT47">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Hungary NB I</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Paksi SE</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Ferencváros</t>
-        </is>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Hungary NB I</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Vasas</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Győri ETO</t>
-        </is>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>0</v>
-      </c>
-      <c r="AK50">
-        <v>0</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
-      <c r="AR50">
-        <v>0</v>
-      </c>
-      <c r="AS50">
-        <v>0</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <v>0</v>
-      </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0</v>
-      </c>
-      <c r="AG51">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>0</v>
-      </c>
-      <c r="AK51">
-        <v>0</v>
-      </c>
-      <c r="AL51">
-        <v>0</v>
-      </c>
-      <c r="AM51">
-        <v>-1</v>
-      </c>
-      <c r="AN51">
-        <v>-1</v>
-      </c>
-      <c r="AO51">
-        <v>-1</v>
-      </c>
-      <c r="AP51">
-        <v>-1</v>
-      </c>
-      <c r="AQ51">
-        <v>0</v>
-      </c>
-      <c r="AR51">
-        <v>0</v>
-      </c>
-      <c r="AS51">
-        <v>0</v>
-      </c>
-      <c r="AT51">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52">
-        <v>0</v>
-      </c>
-      <c r="X52">
-        <v>0</v>
-      </c>
-      <c r="Y52">
-        <v>0</v>
-      </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-      <c r="AA52">
-        <v>0</v>
-      </c>
-      <c r="AB52">
-        <v>0</v>
-      </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
-      <c r="AD52">
-        <v>0</v>
-      </c>
-      <c r="AE52">
-        <v>0</v>
-      </c>
-      <c r="AF52">
-        <v>0</v>
-      </c>
-      <c r="AG52">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>0</v>
-      </c>
-      <c r="AK52">
-        <v>0</v>
-      </c>
-      <c r="AL52">
-        <v>0</v>
-      </c>
-      <c r="AM52">
-        <v>-1</v>
-      </c>
-      <c r="AN52">
-        <v>-1</v>
-      </c>
-      <c r="AO52">
-        <v>-1</v>
-      </c>
-      <c r="AP52">
-        <v>-1</v>
-      </c>
-      <c r="AQ52">
-        <v>0</v>
-      </c>
-      <c r="AR52">
-        <v>0</v>
-      </c>
-      <c r="AS52">
-        <v>0</v>
-      </c>
-      <c r="AT52">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Colo-Colo</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>0</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53">
-        <v>0</v>
-      </c>
-      <c r="Y53">
-        <v>0</v>
-      </c>
-      <c r="Z53">
-        <v>0</v>
-      </c>
-      <c r="AA53">
-        <v>0</v>
-      </c>
-      <c r="AB53">
-        <v>0</v>
-      </c>
-      <c r="AC53">
-        <v>0</v>
-      </c>
-      <c r="AD53">
-        <v>0</v>
-      </c>
-      <c r="AE53">
-        <v>0</v>
-      </c>
-      <c r="AF53">
-        <v>0</v>
-      </c>
-      <c r="AG53">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>0</v>
-      </c>
-      <c r="AK53">
-        <v>0</v>
-      </c>
-      <c r="AL53">
-        <v>0</v>
-      </c>
-      <c r="AM53">
-        <v>-1</v>
-      </c>
-      <c r="AN53">
-        <v>-1</v>
-      </c>
-      <c r="AO53">
-        <v>-1</v>
-      </c>
-      <c r="AP53">
-        <v>-1</v>
-      </c>
-      <c r="AQ53">
-        <v>0</v>
-      </c>
-      <c r="AR53">
-        <v>0</v>
-      </c>
-      <c r="AS53">
-        <v>0</v>
-      </c>
-      <c r="AT53">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
-      <c r="V54">
-        <v>0</v>
-      </c>
-      <c r="W54">
-        <v>0</v>
-      </c>
-      <c r="X54">
-        <v>0</v>
-      </c>
-      <c r="Y54">
-        <v>0</v>
-      </c>
-      <c r="Z54">
-        <v>0</v>
-      </c>
-      <c r="AA54">
-        <v>0</v>
-      </c>
-      <c r="AB54">
-        <v>0</v>
-      </c>
-      <c r="AC54">
-        <v>0</v>
-      </c>
-      <c r="AD54">
-        <v>0</v>
-      </c>
-      <c r="AE54">
-        <v>0</v>
-      </c>
-      <c r="AF54">
-        <v>0</v>
-      </c>
-      <c r="AG54">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>0</v>
-      </c>
-      <c r="AK54">
-        <v>0</v>
-      </c>
-      <c r="AL54">
-        <v>0</v>
-      </c>
-      <c r="AM54">
-        <v>-1</v>
-      </c>
-      <c r="AN54">
-        <v>-1</v>
-      </c>
-      <c r="AO54">
-        <v>-1</v>
-      </c>
-      <c r="AP54">
-        <v>-1</v>
-      </c>
-      <c r="AQ54">
-        <v>0</v>
-      </c>
-      <c r="AR54">
-        <v>0</v>
-      </c>
-      <c r="AS54">
-        <v>0</v>
-      </c>
-      <c r="AT54">
-        <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>2026-07-24 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-      <c r="U55">
-        <v>0</v>
-      </c>
-      <c r="V55">
-        <v>0</v>
-      </c>
-      <c r="W55">
-        <v>0</v>
-      </c>
-      <c r="X55">
-        <v>0</v>
-      </c>
-      <c r="Y55">
-        <v>0</v>
-      </c>
-      <c r="Z55">
-        <v>0</v>
-      </c>
-      <c r="AA55">
-        <v>0</v>
-      </c>
-      <c r="AB55">
-        <v>0</v>
-      </c>
-      <c r="AC55">
-        <v>0</v>
-      </c>
-      <c r="AD55">
-        <v>0</v>
-      </c>
-      <c r="AE55">
-        <v>0</v>
-      </c>
-      <c r="AF55">
-        <v>0</v>
-      </c>
-      <c r="AG55">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>0</v>
-      </c>
-      <c r="AK55">
-        <v>0</v>
-      </c>
-      <c r="AL55">
-        <v>0</v>
-      </c>
-      <c r="AM55">
-        <v>-1</v>
-      </c>
-      <c r="AN55">
-        <v>-1</v>
-      </c>
-      <c r="AO55">
-        <v>-1</v>
-      </c>
-      <c r="AP55">
-        <v>-1</v>
-      </c>
-      <c r="AQ55">
-        <v>0</v>
-      </c>
-      <c r="AR55">
-        <v>0</v>
-      </c>
-      <c r="AS55">
-        <v>0</v>
-      </c>
-      <c r="AT55">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
         <is>
           <t>2026-07-24 23:00:00</t>
         </is>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -3406,58 +3406,58 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U19">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
         <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA19">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC19">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AD19">
         <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
         <v>1.64</v>
@@ -3479,7 +3479,7 @@
         <v>1.5</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="O20">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="P20">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -3587,7 +3587,7 @@
         <v>1.52</v>
       </c>
       <c r="T20">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U20">
         <v>3.4</v>
@@ -3596,16 +3596,16 @@
         <v>1.25</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z20">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AA20">
         <v>2.55</v>
@@ -3614,19 +3614,19 @@
         <v>1.51</v>
       </c>
       <c r="AC20">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AD20">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AE20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG20">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
         <v>1.62</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="O23">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="Q23">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="S23">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA23">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AC23">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD23">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AK23">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="O24">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="P24">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q24">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="R24">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="V24">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24">
         <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB24">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AC24">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -644,55 +644,55 @@
         <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>2.05</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
         <v>2.56</v>
@@ -825,7 +825,7 @@
         <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.04</v>
@@ -837,13 +837,13 @@
         <v>3</v>
       </c>
       <c r="AA3">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD3">
         <v>1.21</v>
@@ -855,7 +855,7 @@
         <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>1.53</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
         <v>4.6</v>
@@ -973,22 +973,22 @@
         <v>2</v>
       </c>
       <c r="R4">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="S4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U4">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1000,19 +1000,19 @@
         <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB4">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AC4">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AD4">
         <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
         <v>1.65</v>
@@ -1034,7 +1034,7 @@
         <v>1.14</v>
       </c>
       <c r="AK4">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="O6">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="P6">
-        <v>4.47</v>
+        <v>3.74</v>
       </c>
       <c r="Q6">
         <v>2.41</v>
@@ -1302,10 +1302,10 @@
         <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U6">
         <v>2.36</v>
@@ -1326,7 +1326,7 @@
         <v>4.2</v>
       </c>
       <c r="AA6">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB6">
         <v>2.07</v>
@@ -1341,10 +1341,10 @@
         <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
         <v>1.82</v>
@@ -2591,61 +2591,61 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>5.81</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>1.95</v>
       </c>
       <c r="R14">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
         <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
         <v>1.6</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="AA14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="AC14">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AD14">
+        <v>1.6</v>
+      </c>
+      <c r="AE14">
+        <v>1.19</v>
+      </c>
+      <c r="AF14">
         <v>1.57</v>
-      </c>
-      <c r="AE14">
-        <v>1.17</v>
-      </c>
-      <c r="AF14">
-        <v>1.67</v>
       </c>
       <c r="AG14">
         <v>2.1</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>4.94</v>
+        <v>3.85</v>
       </c>
       <c r="Q15">
         <v>2.45</v>
       </c>
       <c r="R15">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T15">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="U15">
         <v>3.2</v>
@@ -2784,34 +2784,34 @@
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
         <v>2.95</v>
       </c>
       <c r="AA15">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG15">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="P16">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="Q16">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S16">
         <v>1.29</v>
@@ -2938,16 +2938,16 @@
         <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V16">
         <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.2</v>
@@ -2956,22 +2956,22 @@
         <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
         <v>2.25</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>5.24</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
         <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U18">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
         <v>1.03</v>
@@ -3282,41 +3282,41 @@
         <v>2.97</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB18">
         <v>1.75</v>
       </c>
       <c r="AC18">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
+        <v>1.94</v>
+      </c>
+      <c r="AG18">
+        <v>1.77</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.27</v>
+      </c>
+      <c r="AK18">
         <v>2.1</v>
-      </c>
-      <c r="AG18">
-        <v>1.67</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.25</v>
-      </c>
-      <c r="AK18">
-        <v>2.18</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q19">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="U19">
         <v>2.74</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
         <v>1.84</v>
       </c>
       <c r="AB19">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AC19">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
         <v>1.38</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O20">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -3587,25 +3587,25 @@
         <v>1.52</v>
       </c>
       <c r="T20">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U20">
         <v>3.4</v>
       </c>
       <c r="V20">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W20">
         <v>1.02</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y20">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z20">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AA20">
         <v>2.55</v>
@@ -3614,10 +3614,10 @@
         <v>1.51</v>
       </c>
       <c r="AC20">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AD20">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE20">
         <v>1.02</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK20">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="O21">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>4.92</v>
+        <v>4.33</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P22">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="Q22">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U22">
         <v>2.38</v>
@@ -3934,10 +3934,10 @@
         <v>4.15</v>
       </c>
       <c r="AA22">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB22">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC22">
         <v>2.56</v>
@@ -3946,7 +3946,7 @@
         <v>1.4</v>
       </c>
       <c r="AE22">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
         <v>1.46</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q23">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="R23">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="S23">
         <v>1.27</v>
@@ -4085,37 +4085,37 @@
         <v>1.49</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA23">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB23">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
         <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AK23">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,22 +4221,22 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
         <v>2.7</v>
@@ -4245,7 +4245,7 @@
         <v>2.78</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
         <v>1.08</v>
@@ -4260,25 +4260,25 @@
         <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AD24">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
         <v>1.68</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AK24">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,49 +4547,49 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O26">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>4.83</v>
+        <v>5.11</v>
       </c>
       <c r="Q26">
         <v>2.07</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
         <v>4.32</v>
       </c>
       <c r="AA26">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB26">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC26">
         <v>2.65</v>
@@ -4601,7 +4601,7 @@
         <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
         <v>2.04</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
         <v>2.33</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="O27">
-        <v>5.6</v>
+        <v>7.05</v>
       </c>
       <c r="P27">
-        <v>8.15</v>
+        <v>9.5</v>
       </c>
       <c r="Q27">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U27">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V27">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X27">
         <v>0</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA27">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AB27">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="AC27">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AD27">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AE27">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AF27">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AG27">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.09</v>
       </c>
       <c r="AK27">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,19 +4882,19 @@
         <v>2.83</v>
       </c>
       <c r="Q28">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S28">
         <v>1.48</v>
       </c>
       <c r="T28">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V28">
         <v>1.31</v>
@@ -4903,22 +4903,22 @@
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
         <v>1.35</v>
       </c>
       <c r="Z28">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB28">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC28">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AD28">
         <v>1.19</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
         <v>1.3</v>
@@ -5552,37 +5552,37 @@
         <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>3.8</v>
+        <v>4.04</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB32">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
         <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="R33">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="S33">
         <v>1.17</v>
@@ -5709,7 +5709,7 @@
         <v>4.4</v>
       </c>
       <c r="U33">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V33">
         <v>1.73</v>
@@ -5727,25 +5727,25 @@
         <v>5.75</v>
       </c>
       <c r="AA33">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB33">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AC33">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD33">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF33">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG33">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.14</v>
       </c>
       <c r="AK33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6675,25 +6675,25 @@
         <v>6.65</v>
       </c>
       <c r="Q39">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R39">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S39">
         <v>1.22</v>
       </c>
       <c r="T39">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U39">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="V39">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6705,25 +6705,25 @@
         <v>5.2</v>
       </c>
       <c r="AA39">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AB39">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AC39">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD39">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK39">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6841,19 +6841,19 @@
         <v>3.12</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
         <v>1.33</v>
       </c>
       <c r="T40">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="U40">
         <v>2.67</v>
       </c>
       <c r="V40">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W40">
         <v>1.07</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="AA40">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB40">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AC40">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD40">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE40">
         <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AK40">
         <v>1.41</v>
@@ -7158,10 +7158,10 @@
         <v>1.45</v>
       </c>
       <c r="O42">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>6.13</v>
+        <v>5.5</v>
       </c>
       <c r="Q42">
         <v>1.94</v>
@@ -7170,13 +7170,13 @@
         <v>2.5</v>
       </c>
       <c r="S42">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="U42">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V42">
         <v>1.56</v>
@@ -7188,31 +7188,31 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA42">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AC42">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AD42">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF42">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P23">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q23">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="R23">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="S23">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="V23">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA23">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC23">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG23">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AK23">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="R24">
-        <v>1.99</v>
+        <v>2.34</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
+        <v>3.25</v>
+      </c>
+      <c r="U24">
+        <v>2.54</v>
+      </c>
+      <c r="V24">
+        <v>1.49</v>
+      </c>
+      <c r="W24">
+        <v>1.11</v>
+      </c>
+      <c r="X24">
+        <v>1.03</v>
+      </c>
+      <c r="Y24">
+        <v>1.17</v>
+      </c>
+      <c r="Z24">
+        <v>4</v>
+      </c>
+      <c r="AA24">
+        <v>1.69</v>
+      </c>
+      <c r="AB24">
+        <v>2.1</v>
+      </c>
+      <c r="AC24">
         <v>2.7</v>
       </c>
-      <c r="U24">
-        <v>2.78</v>
-      </c>
-      <c r="V24">
+      <c r="AD24">
         <v>1.36</v>
       </c>
-      <c r="W24">
-        <v>1.08</v>
-      </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1.25</v>
-      </c>
-      <c r="Z24">
-        <v>3.28</v>
-      </c>
-      <c r="AA24">
-        <v>1.9</v>
-      </c>
-      <c r="AB24">
-        <v>1.8</v>
-      </c>
-      <c r="AC24">
-        <v>3.32</v>
-      </c>
-      <c r="AD24">
-        <v>1.26</v>
-      </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q23">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="R23">
-        <v>1.99</v>
+        <v>2.34</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
+        <v>3.25</v>
+      </c>
+      <c r="U23">
+        <v>2.54</v>
+      </c>
+      <c r="V23">
+        <v>1.49</v>
+      </c>
+      <c r="W23">
+        <v>1.11</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.17</v>
+      </c>
+      <c r="Z23">
+        <v>4</v>
+      </c>
+      <c r="AA23">
+        <v>1.69</v>
+      </c>
+      <c r="AB23">
+        <v>2.1</v>
+      </c>
+      <c r="AC23">
         <v>2.7</v>
       </c>
-      <c r="U23">
-        <v>2.78</v>
-      </c>
-      <c r="V23">
+      <c r="AD23">
         <v>1.36</v>
       </c>
-      <c r="W23">
-        <v>1.08</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>1.25</v>
-      </c>
-      <c r="Z23">
-        <v>3.28</v>
-      </c>
-      <c r="AA23">
-        <v>1.9</v>
-      </c>
-      <c r="AB23">
-        <v>1.8</v>
-      </c>
-      <c r="AC23">
-        <v>3.32</v>
-      </c>
-      <c r="AD23">
-        <v>1.26</v>
-      </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG23">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AK23">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="V24">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG24">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AK24">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q43">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU44"/>
+  <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,25 +644,25 @@
         <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="R2">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
         <v>3.14</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -671,16 +671,16 @@
         <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AD2">
         <v>1.38</v>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-07-24 12:30:00</t>
+          <t>2026-07-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="O6">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>3.74</v>
+        <v>3.18</v>
       </c>
       <c r="Q6">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-07-24 13:00:00</t>
+          <t>2026-07-24 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P7">
+        <v>3.74</v>
+      </c>
+      <c r="Q7">
         <v>2.41</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8">
@@ -1616,10 +1616,10 @@
         <v>2.55</v>
       </c>
       <c r="O8">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13">
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-07-24 14:00:00</t>
+          <t>2026-07-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="R15">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>2.73</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>2.95</v>
+        <v>5.05</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC15">
-        <v>3.74</v>
+        <v>2.4</v>
       </c>
       <c r="AD15">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AF15">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="O16">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="U16">
-        <v>2.41</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>2.51</v>
+        <v>3.74</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="P17">
-        <v>3.01</v>
+        <v>3.88</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-07-24 15:00:00</t>
+          <t>2026-07-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>3.01</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AB18">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC18">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:15:00</t>
+          <t>2026-07-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,81 +3406,81 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>1.72</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>3.06</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>3.09</v>
+        <v>2.69</v>
       </c>
       <c r="U19">
-        <v>2.74</v>
+        <v>3.21</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
+        <v>1.3</v>
+      </c>
+      <c r="Z19">
+        <v>2.97</v>
+      </c>
+      <c r="AA19">
+        <v>2.05</v>
+      </c>
+      <c r="AB19">
+        <v>1.75</v>
+      </c>
+      <c r="AC19">
+        <v>3.75</v>
+      </c>
+      <c r="AD19">
         <v>1.26</v>
       </c>
-      <c r="Z19">
-        <v>3.5</v>
-      </c>
-      <c r="AA19">
-        <v>1.84</v>
-      </c>
-      <c r="AB19">
-        <v>1.92</v>
-      </c>
-      <c r="AC19">
-        <v>2.97</v>
-      </c>
-      <c r="AD19">
-        <v>1.3</v>
-      </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AG19">
+        <v>1.77</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.27</v>
+      </c>
+      <c r="AK19">
         <v>2.1</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.29</v>
-      </c>
-      <c r="AK19">
-        <v>1.38</v>
-      </c>
       <c r="AL19">
         <v>0</v>
       </c>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:30:00</t>
+          <t>2026-07-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>3.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="R20">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="S20">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>2.36</v>
+        <v>3.09</v>
       </c>
       <c r="U20">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="V20">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="Z20">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA20">
-        <v>2.55</v>
+        <v>1.84</v>
       </c>
       <c r="AB20">
-        <v>1.51</v>
+        <v>1.92</v>
       </c>
       <c r="AC20">
-        <v>4.9</v>
+        <v>2.97</v>
       </c>
       <c r="AD20">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AG20">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>3.46</v>
+      </c>
+      <c r="Q21">
+        <v>2.75</v>
+      </c>
+      <c r="R21">
+        <v>1.95</v>
+      </c>
+      <c r="S21">
+        <v>1.52</v>
+      </c>
+      <c r="T21">
+        <v>2.36</v>
+      </c>
+      <c r="U21">
         <v>3.4</v>
       </c>
-      <c r="P21">
-        <v>4.33</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:45:00</t>
+          <t>2026-07-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.49</v>
+        <v>1.69</v>
       </c>
       <c r="O22">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q22">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC22">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="P23">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q23">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="R23">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="U23">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="AD23">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AG23">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="V24">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG24">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AK24">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.68</v>
+        <v>3.07</v>
       </c>
       <c r="O25">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-07-24 16:00:00</t>
+          <t>2026-07-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="P26">
-        <v>5.11</v>
+        <v>2.31</v>
       </c>
       <c r="Q26">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
+        <v>1.55</v>
+      </c>
+      <c r="O27">
+        <v>3.9</v>
+      </c>
+      <c r="P27">
+        <v>5.11</v>
+      </c>
+      <c r="Q27">
+        <v>2.07</v>
+      </c>
+      <c r="R27">
+        <v>2.34</v>
+      </c>
+      <c r="S27">
+        <v>1.3</v>
+      </c>
+      <c r="T27">
+        <v>3.22</v>
+      </c>
+      <c r="U27">
+        <v>2.44</v>
+      </c>
+      <c r="V27">
+        <v>1.49</v>
+      </c>
+      <c r="W27">
+        <v>1.08</v>
+      </c>
+      <c r="X27">
+        <v>1.04</v>
+      </c>
+      <c r="Y27">
+        <v>1.21</v>
+      </c>
+      <c r="Z27">
+        <v>4.32</v>
+      </c>
+      <c r="AA27">
+        <v>1.66</v>
+      </c>
+      <c r="AB27">
+        <v>2.15</v>
+      </c>
+      <c r="AC27">
+        <v>2.65</v>
+      </c>
+      <c r="AD27">
+        <v>1.4</v>
+      </c>
+      <c r="AE27">
         <v>1.16</v>
       </c>
-      <c r="O27">
-        <v>7.05</v>
-      </c>
-      <c r="P27">
-        <v>9.5</v>
-      </c>
-      <c r="Q27">
-        <v>1.51</v>
-      </c>
-      <c r="R27">
-        <v>3.18</v>
-      </c>
-      <c r="S27">
-        <v>1.13</v>
-      </c>
-      <c r="T27">
-        <v>5.25</v>
-      </c>
-      <c r="U27">
-        <v>1.79</v>
-      </c>
-      <c r="V27">
-        <v>1.97</v>
-      </c>
-      <c r="W27">
-        <v>1.26</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>1.02</v>
-      </c>
-      <c r="Z27">
-        <v>7.9</v>
-      </c>
-      <c r="AA27">
-        <v>1.23</v>
-      </c>
-      <c r="AB27">
-        <v>3.83</v>
-      </c>
-      <c r="AC27">
-        <v>1.67</v>
-      </c>
-      <c r="AD27">
-        <v>2.14</v>
-      </c>
-      <c r="AE27">
-        <v>1.48</v>
-      </c>
       <c r="AF27">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>4.33</v>
+        <v>2.33</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-07-24 17:00:00</t>
+          <t>2026-07-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>1.16</v>
       </c>
       <c r="O28">
-        <v>3.02</v>
+        <v>7.05</v>
       </c>
       <c r="P28">
-        <v>2.83</v>
+        <v>9.5</v>
       </c>
       <c r="Q28">
-        <v>3.24</v>
+        <v>1.51</v>
       </c>
       <c r="R28">
-        <v>1.92</v>
+        <v>3.18</v>
       </c>
       <c r="S28">
+        <v>1.13</v>
+      </c>
+      <c r="T28">
+        <v>5.25</v>
+      </c>
+      <c r="U28">
+        <v>1.79</v>
+      </c>
+      <c r="V28">
+        <v>1.97</v>
+      </c>
+      <c r="W28">
+        <v>1.26</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>1.02</v>
+      </c>
+      <c r="Z28">
+        <v>7.9</v>
+      </c>
+      <c r="AA28">
+        <v>1.23</v>
+      </c>
+      <c r="AB28">
+        <v>3.83</v>
+      </c>
+      <c r="AC28">
+        <v>1.67</v>
+      </c>
+      <c r="AD28">
+        <v>2.14</v>
+      </c>
+      <c r="AE28">
         <v>1.48</v>
       </c>
-      <c r="T28">
-        <v>2.75</v>
-      </c>
-      <c r="U28">
-        <v>3.1</v>
-      </c>
-      <c r="V28">
-        <v>1.31</v>
-      </c>
-      <c r="W28">
-        <v>1.04</v>
-      </c>
-      <c r="X28">
-        <v>1.06</v>
-      </c>
-      <c r="Y28">
-        <v>1.35</v>
-      </c>
-      <c r="Z28">
-        <v>3.08</v>
-      </c>
-      <c r="AA28">
-        <v>2.15</v>
-      </c>
-      <c r="AB28">
-        <v>1.66</v>
-      </c>
-      <c r="AC28">
-        <v>4</v>
-      </c>
-      <c r="AD28">
-        <v>1.19</v>
-      </c>
-      <c r="AE28">
-        <v>1.03</v>
-      </c>
       <c r="AF28">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="AK28">
-        <v>1.47</v>
+        <v>4.33</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-07-24 19:00:00</t>
+          <t>2026-07-24 17:00:00</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3.56</v>
+        <v>3.02</v>
       </c>
       <c r="P29">
-        <v>4.13</v>
+        <v>2.83</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-07-24 20:00:00</t>
+          <t>2026-07-24 19:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G32">
@@ -5521,68 +5521,68 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N32">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q33">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
+        <v>1.3</v>
+      </c>
+      <c r="T33">
+        <v>3.08</v>
+      </c>
+      <c r="U33">
+        <v>2.41</v>
+      </c>
+      <c r="V33">
+        <v>1.47</v>
+      </c>
+      <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
         <v>1.17</v>
       </c>
-      <c r="T33">
-        <v>4.4</v>
-      </c>
-      <c r="U33">
-        <v>2.04</v>
-      </c>
-      <c r="V33">
-        <v>1.73</v>
-      </c>
-      <c r="W33">
-        <v>1.2</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.07</v>
-      </c>
       <c r="Z33">
-        <v>5.75</v>
+        <v>4.04</v>
       </c>
       <c r="AA33">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AB33">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="AD33">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.13</v>
+        <v>1.72</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G34">
@@ -5860,55 +5860,55 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.35</v>
+        <v>3.29</v>
       </c>
       <c r="O39">
-        <v>4.75</v>
+        <v>3.22</v>
       </c>
       <c r="P39">
-        <v>6.65</v>
+        <v>2.06</v>
       </c>
       <c r="Q39">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 23:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6932,658 +6932,6 @@
         <v>0</v>
       </c>
       <c r="AU40" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <v>0</v>
-      </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <v>0</v>
-      </c>
-      <c r="AB41">
-        <v>0</v>
-      </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
-      <c r="AK41">
-        <v>0</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
-      <c r="AM41">
-        <v>-1</v>
-      </c>
-      <c r="AN41">
-        <v>-1</v>
-      </c>
-      <c r="AO41">
-        <v>-1</v>
-      </c>
-      <c r="AP41">
-        <v>-1</v>
-      </c>
-      <c r="AQ41">
-        <v>0</v>
-      </c>
-      <c r="AR41">
-        <v>0</v>
-      </c>
-      <c r="AS41">
-        <v>0</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Colo-Colo</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N42">
-        <v>1.45</v>
-      </c>
-      <c r="O42">
-        <v>4.2</v>
-      </c>
-      <c r="P42">
-        <v>5.5</v>
-      </c>
-      <c r="Q42">
-        <v>1.94</v>
-      </c>
-      <c r="R42">
-        <v>2.5</v>
-      </c>
-      <c r="S42">
-        <v>1.25</v>
-      </c>
-      <c r="T42">
-        <v>3.45</v>
-      </c>
-      <c r="U42">
-        <v>2.2</v>
-      </c>
-      <c r="V42">
-        <v>1.56</v>
-      </c>
-      <c r="W42">
-        <v>1.13</v>
-      </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
-      <c r="Y42">
-        <v>1.18</v>
-      </c>
-      <c r="Z42">
-        <v>4.75</v>
-      </c>
-      <c r="AA42">
-        <v>1.6</v>
-      </c>
-      <c r="AB42">
-        <v>2.38</v>
-      </c>
-      <c r="AC42">
-        <v>2.35</v>
-      </c>
-      <c r="AD42">
-        <v>1.53</v>
-      </c>
-      <c r="AE42">
-        <v>1.21</v>
-      </c>
-      <c r="AF42">
-        <v>1.65</v>
-      </c>
-      <c r="AG42">
-        <v>2</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.16</v>
-      </c>
-      <c r="AK42">
-        <v>2.46</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>-1</v>
-      </c>
-      <c r="AN42">
-        <v>-1</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>-1</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>2026-07-24 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N43">
-        <v>3.29</v>
-      </c>
-      <c r="O43">
-        <v>3.22</v>
-      </c>
-      <c r="P43">
-        <v>2.06</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>-1</v>
-      </c>
-      <c r="AN43">
-        <v>-1</v>
-      </c>
-      <c r="AO43">
-        <v>-1</v>
-      </c>
-      <c r="AP43">
-        <v>-1</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
-      <c r="AS43">
-        <v>0</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>2026-07-24 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>0</v>
-      </c>
-      <c r="Y44">
-        <v>0</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>0</v>
-      </c>
-      <c r="AB44">
-        <v>0</v>
-      </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
-      <c r="AD44">
-        <v>0</v>
-      </c>
-      <c r="AE44">
-        <v>0</v>
-      </c>
-      <c r="AF44">
-        <v>0</v>
-      </c>
-      <c r="AG44">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>0</v>
-      </c>
-      <c r="AK44">
-        <v>0</v>
-      </c>
-      <c r="AL44">
-        <v>0</v>
-      </c>
-      <c r="AM44">
-        <v>-1</v>
-      </c>
-      <c r="AN44">
-        <v>-1</v>
-      </c>
-      <c r="AO44">
-        <v>-1</v>
-      </c>
-      <c r="AP44">
-        <v>-1</v>
-      </c>
-      <c r="AQ44">
-        <v>0</v>
-      </c>
-      <c r="AR44">
-        <v>0</v>
-      </c>
-      <c r="AS44">
-        <v>0</v>
-      </c>
-      <c r="AT44">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
         <is>
           <t>2026-07-24 23:00:00</t>
         </is>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="O6">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P6">
-        <v>3.18</v>
+        <v>3.49</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1456,28 +1456,28 @@
         <v>3.58</v>
       </c>
       <c r="P7">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="Q7">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T7">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V7">
         <v>1.49</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1486,28 +1486,28 @@
         <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG7">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="O9">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="P9">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA9">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G10">
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11">
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12">
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2920,28 +2920,28 @@
         <v>2.05</v>
       </c>
       <c r="O16">
+        <v>3.1</v>
+      </c>
+      <c r="P16">
         <v>3.25</v>
       </c>
-      <c r="P16">
-        <v>3.85</v>
-      </c>
       <c r="Q16">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="R16">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="T16">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="U16">
         <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2953,28 +2953,28 @@
         <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AA16">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC16">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE16">
         <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG16">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O17">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="Q17">
+        <v>2.32</v>
+      </c>
+      <c r="R17">
+        <v>2.21</v>
+      </c>
+      <c r="S17">
+        <v>1.31</v>
+      </c>
+      <c r="T17">
+        <v>3.15</v>
+      </c>
+      <c r="U17">
         <v>2.4</v>
-      </c>
-      <c r="R17">
-        <v>2.24</v>
-      </c>
-      <c r="S17">
-        <v>1.29</v>
-      </c>
-      <c r="T17">
-        <v>3.25</v>
-      </c>
-      <c r="U17">
-        <v>2.41</v>
       </c>
       <c r="V17">
         <v>1.5</v>
@@ -3110,31 +3110,31 @@
         <v>1.09</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB17">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC17">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG17">
         <v>2.25</v>
@@ -3153,7 +3153,7 @@
         <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,61 +3246,61 @@
         <v>2.09</v>
       </c>
       <c r="O18">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA18">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AB18">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S19">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
+        <v>1.04</v>
+      </c>
+      <c r="X19">
         <v>1.05</v>
       </c>
-      <c r="X19">
-        <v>1.03</v>
-      </c>
       <c r="Y19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>2.97</v>
+        <v>3.37</v>
       </c>
       <c r="AA19">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC19">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AD19">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AG19">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>3.06</v>
+        <v>3.66</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z20">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA20">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AB20">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC20">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD20">
         <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK20">
         <v>1.38</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
         <v>3</v>
       </c>
       <c r="P21">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S21">
         <v>1.52</v>
       </c>
       <c r="T21">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U21">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="V21">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z21">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA21">
         <v>2.55</v>
       </c>
       <c r="AB21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC21">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AD21">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF21">
         <v>2.08</v>
       </c>
       <c r="AG21">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="O26">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB26">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5860,22 +5860,22 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>4.33</v>
+        <v>4.86</v>
       </c>
       <c r="R34">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="S34">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V34">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W34">
         <v>1.2</v>
@@ -5884,31 +5884,31 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>5.75</v>
+        <v>6.31</v>
       </c>
       <c r="AA34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB34">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AC34">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD34">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE34">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF34">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AG34">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK34">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -635,55 +635,55 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
         <v>3.14</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
         <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AD2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE2">
         <v>1.11</v>
@@ -692,7 +692,7 @@
         <v>1.56</v>
       </c>
       <c r="AG2">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S3">
         <v>1.42</v>
@@ -819,7 +819,7 @@
         <v>2.56</v>
       </c>
       <c r="U3">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="V3">
         <v>1.32</v>
@@ -834,22 +834,22 @@
         <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
         <v>1.83</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
         <v>1.3</v>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T4">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1000,16 +1000,16 @@
         <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB4">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AC4">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE4">
         <v>1.14</v>
@@ -1018,7 +1018,7 @@
         <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
         <v>2.41</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G11">
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.85</v>
+        <v>1.94</v>
       </c>
       <c r="R11">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T11">
         <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
         <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AD11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>1.51</v>
+        <v>2.49</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G12">
@@ -2274,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
         <v>3.2</v>
@@ -2289,7 +2289,7 @@
         <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2298,31 +2298,31 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
         <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC12">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AG12">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>1.94</v>
+        <v>2.85</v>
       </c>
       <c r="R13">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="S13">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
         <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AA13">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB13">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AD13">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE13">
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>2.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,13 +2600,13 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
         <v>3.2</v>
@@ -2615,7 +2615,7 @@
         <v>2.56</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
         <v>1.06</v>
@@ -2624,31 +2624,31 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
         <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB14">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC14">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,61 +2754,61 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q15">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z15">
         <v>5.05</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC15">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG15">
         <v>2.1</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3421,34 +3421,34 @@
         <v>2.14</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="U19">
         <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
         <v>3.37</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB19">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC19">
         <v>3.55</v>
@@ -3460,7 +3460,7 @@
         <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
         <v>1.65</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3895,43 +3895,43 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA22">
         <v>1.9</v>
@@ -3940,19 +3940,19 @@
         <v>1.9</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q23">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
+        <v>1.03</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1.25</v>
+      </c>
+      <c r="Z23">
+        <v>3.45</v>
+      </c>
+      <c r="AA23">
+        <v>1.9</v>
+      </c>
+      <c r="AB23">
+        <v>1.85</v>
+      </c>
+      <c r="AC23">
+        <v>3.1</v>
+      </c>
+      <c r="AD23">
+        <v>1.26</v>
+      </c>
+      <c r="AE23">
         <v>1.11</v>
       </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.16</v>
-      </c>
-      <c r="Z23">
-        <v>4.15</v>
-      </c>
-      <c r="AA23">
-        <v>1.65</v>
-      </c>
-      <c r="AB23">
-        <v>2.1</v>
-      </c>
-      <c r="AC23">
-        <v>2.56</v>
-      </c>
-      <c r="AD23">
-        <v>1.4</v>
-      </c>
-      <c r="AE23">
-        <v>1.12</v>
-      </c>
       <c r="AF23">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AG23">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
+        <v>2</v>
+      </c>
+      <c r="Q24">
+        <v>3.55</v>
+      </c>
+      <c r="R24">
+        <v>2.3</v>
+      </c>
+      <c r="S24">
+        <v>1.3</v>
+      </c>
+      <c r="T24">
+        <v>3.2</v>
+      </c>
+      <c r="U24">
         <v>2.5</v>
       </c>
-      <c r="Q24">
-        <v>3.34</v>
-      </c>
-      <c r="R24">
-        <v>1.99</v>
-      </c>
-      <c r="S24">
-        <v>1.38</v>
-      </c>
-      <c r="T24">
-        <v>2.7</v>
-      </c>
-      <c r="U24">
-        <v>2.78</v>
-      </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>3.28</v>
+        <v>3.94</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC24">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="AD24">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG24">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q25">
-        <v>3.33</v>
+        <v>3.09</v>
       </c>
       <c r="R25">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
         <v>3.25</v>
       </c>
       <c r="U25">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V25">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
+        <v>1.22</v>
+      </c>
+      <c r="Z25">
+        <v>4.15</v>
+      </c>
+      <c r="AA25">
+        <v>1.65</v>
+      </c>
+      <c r="AB25">
+        <v>2.11</v>
+      </c>
+      <c r="AC25">
+        <v>2.56</v>
+      </c>
+      <c r="AD25">
+        <v>1.4</v>
+      </c>
+      <c r="AE25">
         <v>1.17</v>
       </c>
-      <c r="Z25">
-        <v>4</v>
-      </c>
-      <c r="AA25">
-        <v>1.69</v>
-      </c>
-      <c r="AB25">
-        <v>2.1</v>
-      </c>
-      <c r="AC25">
-        <v>2.7</v>
-      </c>
-      <c r="AD25">
-        <v>1.36</v>
-      </c>
-      <c r="AE25">
-        <v>1.1</v>
-      </c>
       <c r="AF25">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG25">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AK25">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4713,40 +4713,40 @@
         <v>1.55</v>
       </c>
       <c r="O27">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
         <v>5.11</v>
       </c>
       <c r="Q27">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="R27">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U27">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
         <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>4.32</v>
+        <v>3.88</v>
       </c>
       <c r="AA27">
         <v>1.66</v>
@@ -4755,19 +4755,19 @@
         <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE27">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG27">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="O28">
-        <v>7.05</v>
+        <v>5.7</v>
       </c>
       <c r="P28">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="Q28">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R28">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="S28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T28">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="U28">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V28">
         <v>1.97</v>
       </c>
       <c r="W28">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.02</v>
       </c>
       <c r="Z28">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AA28">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AB28">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="AC28">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AD28">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AE28">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF28">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK28">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O29">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="P29">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="Q29">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R29">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T29">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U29">
         <v>3.1</v>
@@ -5072,29 +5072,29 @@
         <v>1.35</v>
       </c>
       <c r="Z29">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AA29">
         <v>2.15</v>
       </c>
       <c r="AB29">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
+        <v>1.83</v>
+      </c>
+      <c r="AG29">
         <v>1.85</v>
       </c>
-      <c r="AG29">
-        <v>1.75</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
         <v>1.47</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O30">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>4.13</v>
+        <v>3.6</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="O33">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U33">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
         <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.04</v>
+        <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC33">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="AD33">
         <v>1.37</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
         <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6023,71 +6023,71 @@
         <v>6.65</v>
       </c>
       <c r="Q35">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R35">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="S35">
         <v>1.22</v>
       </c>
       <c r="T35">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="U35">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="V35">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z35">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA35">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AC35">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AD35">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE35">
+        <v>1.23</v>
+      </c>
+      <c r="AF35">
+        <v>1.55</v>
+      </c>
+      <c r="AG35">
+        <v>2.27</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.17</v>
       </c>
-      <c r="AF35">
-        <v>1.53</v>
-      </c>
-      <c r="AG35">
-        <v>1.83</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.11</v>
-      </c>
       <c r="AK35">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>2.65</v>
       </c>
       <c r="Q36">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R36">
         <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T36">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="U36">
-        <v>2.67</v>
+        <v>2.18</v>
       </c>
       <c r="V36">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
+        <v>1.05</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="Y36">
+        <v>1.2</v>
+      </c>
+      <c r="Z36">
+        <v>3.42</v>
+      </c>
+      <c r="AA36">
+        <v>1.83</v>
+      </c>
+      <c r="AB36">
+        <v>1.82</v>
+      </c>
+      <c r="AC36">
+        <v>2.5</v>
+      </c>
+      <c r="AD36">
+        <v>1.28</v>
+      </c>
+      <c r="AE36">
         <v>1.07</v>
       </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.22</v>
-      </c>
-      <c r="Z36">
-        <v>2.75</v>
-      </c>
-      <c r="AA36">
-        <v>1.86</v>
-      </c>
-      <c r="AB36">
-        <v>1.86</v>
-      </c>
-      <c r="AC36">
-        <v>3.2</v>
-      </c>
-      <c r="AD36">
-        <v>1.27</v>
-      </c>
-      <c r="AE36">
-        <v>1.09</v>
-      </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AK36">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,28 +6503,28 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="O38">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P38">
         <v>5.5</v>
       </c>
       <c r="Q38">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R38">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T38">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V38">
         <v>1.56</v>
@@ -6539,28 +6539,28 @@
         <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="AA38">
         <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD38">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE38">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC39">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="R13">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T13">
         <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
         <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA13">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC13">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD13">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S14">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
         <v>3.2</v>
       </c>
       <c r="U14">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
         <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA14">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG14">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S13">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
         <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
         <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA13">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB13">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AD13">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG13">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="R14">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
         <v>3.2</v>
       </c>
       <c r="U14">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
         <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB14">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC14">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD14">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O33">
         <v>3.25</v>
@@ -5697,55 +5697,55 @@
         <v>2.83</v>
       </c>
       <c r="Q33">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U33">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA33">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU40"/>
+  <dimension ref="A1:AU45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,19 +1293,19 @@
         <v>3.26</v>
       </c>
       <c r="P6">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="Q6">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="R6">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="S6">
         <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U6">
         <v>2.9</v>
@@ -1323,25 +1323,25 @@
         <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
         <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
         <v>1.93</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK6">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="Q7">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="U7">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE7">
         <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
         <v>2.2</v>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
         <v>3.28</v>
@@ -1785,28 +1785,28 @@
         <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R9">
         <v>2.35</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="V9">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
         <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
         <v>1.18</v>
@@ -1815,22 +1815,22 @@
         <v>3.92</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC9">
         <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG9">
         <v>2.24</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q10">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="R10">
         <v>2.15</v>
@@ -1957,16 +1957,16 @@
         <v>1.32</v>
       </c>
       <c r="T10">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
         <v>2.56</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -1978,7 +1978,7 @@
         <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
         <v>1.94</v>
@@ -1996,7 +1996,7 @@
         <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
         <v>1.83</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R11">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
         <v>1.27</v>
@@ -2123,7 +2123,7 @@
         <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V11">
         <v>1.46</v>
@@ -2132,10 +2132,10 @@
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
         <v>4.1</v>
@@ -2150,16 +2150,16 @@
         <v>2.63</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R12">
         <v>2.25</v>
@@ -2292,7 +2292,7 @@
         <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -2307,10 +2307,10 @@
         <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AD12">
         <v>1.33</v>
@@ -2319,10 +2319,10 @@
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
         <v>2.18</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,71 +2437,71 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="R13">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="S13">
+        <v>1.35</v>
+      </c>
+      <c r="T13">
+        <v>2.79</v>
+      </c>
+      <c r="U13">
+        <v>2.6</v>
+      </c>
+      <c r="V13">
+        <v>1.38</v>
+      </c>
+      <c r="W13">
+        <v>1.1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>3.42</v>
+      </c>
+      <c r="AA13">
+        <v>1.87</v>
+      </c>
+      <c r="AB13">
+        <v>1.9</v>
+      </c>
+      <c r="AC13">
+        <v>2.97</v>
+      </c>
+      <c r="AD13">
         <v>1.3</v>
       </c>
-      <c r="T13">
-        <v>3.2</v>
-      </c>
-      <c r="U13">
-        <v>2.47</v>
-      </c>
-      <c r="V13">
+      <c r="AE13">
+        <v>1.08</v>
+      </c>
+      <c r="AF13">
+        <v>1.62</v>
+      </c>
+      <c r="AG13">
+        <v>2.2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.44</v>
       </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.17</v>
-      </c>
-      <c r="Z13">
-        <v>3.98</v>
-      </c>
-      <c r="AA13">
-        <v>1.73</v>
-      </c>
-      <c r="AB13">
-        <v>2.1</v>
-      </c>
-      <c r="AC13">
-        <v>2.66</v>
-      </c>
-      <c r="AD13">
-        <v>1.37</v>
-      </c>
-      <c r="AE13">
-        <v>1.11</v>
-      </c>
-      <c r="AF13">
-        <v>1.54</v>
-      </c>
-      <c r="AG13">
-        <v>2.3</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.24</v>
-      </c>
       <c r="AK13">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q14">
+        <v>2.5</v>
+      </c>
+      <c r="R14">
+        <v>2.3</v>
+      </c>
+      <c r="S14">
+        <v>1.29</v>
+      </c>
+      <c r="T14">
         <v>3.25</v>
       </c>
-      <c r="R14">
-        <v>2.05</v>
-      </c>
-      <c r="S14">
-        <v>1.34</v>
-      </c>
-      <c r="T14">
-        <v>3.2</v>
-      </c>
       <c r="U14">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
         <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AA14">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>3.25</v>
+        <v>4.06</v>
       </c>
       <c r="Q16">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S16">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="T16">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="U16">
         <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2956,7 +2956,7 @@
         <v>3.08</v>
       </c>
       <c r="AA16">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AB16">
         <v>1.74</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q17">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R17">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="S17">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
         <v>2.4</v>
@@ -3107,19 +3107,19 @@
         <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
         <v>4.4</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB17">
         <v>2.19</v>
@@ -3131,13 +3131,13 @@
         <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.09</v>
+        <v>1.59</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P18">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="R18">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="U18">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z18">
-        <v>4.15</v>
+        <v>6.4</v>
       </c>
       <c r="AA18">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AC18">
-        <v>2.65</v>
+        <v>1.81</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.28</v>
+        <v>2.79</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:00:00</t>
+          <t>2026-07-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>3.37</v>
+        <v>4.93</v>
       </c>
       <c r="AA19">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="AB19">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>3.55</v>
+        <v>2.31</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK19">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:15:00</t>
+          <t>2026-07-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.48</v>
+        <v>1.59</v>
       </c>
       <c r="O20">
-        <v>3.13</v>
+        <v>4.4</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q20">
-        <v>3.66</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>3.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA20">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AB20">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC20">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD20">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF20">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>2.51</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AK20">
-        <v>1.38</v>
+        <v>2.24</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-07-24 15:30:00</t>
+          <t>2026-07-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="Q21">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="U21">
-        <v>3.52</v>
+        <v>2.38</v>
       </c>
       <c r="V21">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="Z21">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="AA21">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>4.85</v>
+        <v>2.65</v>
       </c>
       <c r="AD21">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:30:00</t>
+          <t>2026-07-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P22">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="Q22">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T22">
-        <v>2.82</v>
+        <v>3.42</v>
       </c>
       <c r="U22">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>3.34</v>
+        <v>5.06</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AC22">
-        <v>3.24</v>
+        <v>2.19</v>
       </c>
       <c r="AD22">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AG22">
-        <v>1.89</v>
+        <v>2.66</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-07-24 15:45:00</t>
+          <t>2026-07-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>2.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R23">
+        <v>2.5</v>
+      </c>
+      <c r="S23">
+        <v>1.19</v>
+      </c>
+      <c r="T23">
+        <v>3.78</v>
+      </c>
+      <c r="U23">
+        <v>2.1</v>
+      </c>
+      <c r="V23">
+        <v>1.65</v>
+      </c>
+      <c r="W23">
+        <v>1.14</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.09</v>
+      </c>
+      <c r="Z23">
+        <v>5.35</v>
+      </c>
+      <c r="AA23">
+        <v>1.44</v>
+      </c>
+      <c r="AB23">
+        <v>2.56</v>
+      </c>
+      <c r="AC23">
         <v>2.08</v>
       </c>
-      <c r="S23">
-        <v>1.38</v>
-      </c>
-      <c r="T23">
-        <v>2.7</v>
-      </c>
-      <c r="U23">
-        <v>2.78</v>
-      </c>
-      <c r="V23">
-        <v>1.4</v>
-      </c>
-      <c r="W23">
-        <v>1.03</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>1.25</v>
-      </c>
-      <c r="Z23">
-        <v>3.45</v>
-      </c>
-      <c r="AA23">
-        <v>1.9</v>
-      </c>
-      <c r="AB23">
-        <v>1.85</v>
-      </c>
-      <c r="AC23">
-        <v>3.1</v>
-      </c>
       <c r="AD23">
+        <v>1.65</v>
+      </c>
+      <c r="AE23">
         <v>1.26</v>
       </c>
-      <c r="AE23">
-        <v>1.11</v>
-      </c>
       <c r="AF23">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="AK23">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-07-24 15:45:00</t>
+          <t>2026-07-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,81 +4221,81 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q24">
+        <v>2.2</v>
+      </c>
+      <c r="R24">
+        <v>2.14</v>
+      </c>
+      <c r="S24">
+        <v>1.41</v>
+      </c>
+      <c r="T24">
+        <v>2.78</v>
+      </c>
+      <c r="U24">
+        <v>2.88</v>
+      </c>
+      <c r="V24">
+        <v>1.38</v>
+      </c>
+      <c r="W24">
+        <v>1.05</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.29</v>
+      </c>
+      <c r="Z24">
+        <v>3.37</v>
+      </c>
+      <c r="AA24">
+        <v>1.99</v>
+      </c>
+      <c r="AB24">
+        <v>1.77</v>
+      </c>
+      <c r="AC24">
         <v>3.55</v>
       </c>
-      <c r="R24">
-        <v>2.3</v>
-      </c>
-      <c r="S24">
-        <v>1.3</v>
-      </c>
-      <c r="T24">
-        <v>3.2</v>
-      </c>
-      <c r="U24">
-        <v>2.5</v>
-      </c>
-      <c r="V24">
-        <v>1.5</v>
-      </c>
-      <c r="W24">
-        <v>1.06</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.22</v>
-      </c>
-      <c r="Z24">
-        <v>3.94</v>
-      </c>
-      <c r="AA24">
-        <v>1.82</v>
-      </c>
-      <c r="AB24">
+      <c r="AD24">
+        <v>1.25</v>
+      </c>
+      <c r="AE24">
+        <v>1.05</v>
+      </c>
+      <c r="AF24">
+        <v>1.91</v>
+      </c>
+      <c r="AG24">
+        <v>1.65</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.25</v>
+      </c>
+      <c r="AK24">
         <v>2.15</v>
       </c>
-      <c r="AC24">
-        <v>3</v>
-      </c>
-      <c r="AD24">
-        <v>1.41</v>
-      </c>
-      <c r="AE24">
-        <v>1.15</v>
-      </c>
-      <c r="AF24">
-        <v>1.66</v>
-      </c>
-      <c r="AG24">
-        <v>2.02</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.21</v>
-      </c>
-      <c r="AK24">
-        <v>1.24</v>
-      </c>
       <c r="AL24">
         <v>0</v>
       </c>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-07-24 15:45:00</t>
+          <t>2026-07-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,81 +4384,81 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O25">
         <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q25">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="U25">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>4.15</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AB25">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>2.56</v>
+        <v>3.42</v>
       </c>
       <c r="AD25">
+        <v>1.3</v>
+      </c>
+      <c r="AE25">
+        <v>1.04</v>
+      </c>
+      <c r="AF25">
+        <v>1.78</v>
+      </c>
+      <c r="AG25">
+        <v>1.94</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.3</v>
+      </c>
+      <c r="AK25">
         <v>1.4</v>
       </c>
-      <c r="AE25">
-        <v>1.17</v>
-      </c>
-      <c r="AF25">
-        <v>1.52</v>
-      </c>
-      <c r="AG25">
-        <v>2.34</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.5</v>
-      </c>
-      <c r="AK25">
-        <v>1.42</v>
-      </c>
       <c r="AL25">
         <v>0</v>
       </c>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-07-24 15:45:00</t>
+          <t>2026-07-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>2.06</v>
+        <v>3.49</v>
       </c>
       <c r="Q26">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="R26">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Z26">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="AA26">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="AC26">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-07-24 16:00:00</t>
+          <t>2026-07-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O27">
+        <v>3.5</v>
+      </c>
+      <c r="P27">
         <v>4.2</v>
       </c>
-      <c r="P27">
-        <v>5.11</v>
-      </c>
       <c r="Q27">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>2.87</v>
+        <v>3.24</v>
       </c>
       <c r="AD27">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG27">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-07-24 16:00:00</t>
+          <t>2026-07-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.27</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>7.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q28">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>3.14</v>
+        <v>2.08</v>
       </c>
       <c r="S28">
+        <v>1.38</v>
+      </c>
+      <c r="T28">
+        <v>2.7</v>
+      </c>
+      <c r="U28">
+        <v>2.78</v>
+      </c>
+      <c r="V28">
+        <v>1.4</v>
+      </c>
+      <c r="W28">
+        <v>1.03</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>1.25</v>
+      </c>
+      <c r="Z28">
+        <v>3.45</v>
+      </c>
+      <c r="AA28">
+        <v>1.9</v>
+      </c>
+      <c r="AB28">
+        <v>1.85</v>
+      </c>
+      <c r="AC28">
+        <v>3.1</v>
+      </c>
+      <c r="AD28">
+        <v>1.26</v>
+      </c>
+      <c r="AE28">
         <v>1.11</v>
       </c>
-      <c r="T28">
-        <v>4.8</v>
-      </c>
-      <c r="U28">
-        <v>1.77</v>
-      </c>
-      <c r="V28">
-        <v>1.97</v>
-      </c>
-      <c r="W28">
-        <v>1.29</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.02</v>
-      </c>
-      <c r="Z28">
-        <v>7.8</v>
-      </c>
-      <c r="AA28">
-        <v>1.18</v>
-      </c>
-      <c r="AB28">
-        <v>3.5</v>
-      </c>
-      <c r="AC28">
-        <v>1.69</v>
-      </c>
-      <c r="AD28">
-        <v>2.11</v>
-      </c>
-      <c r="AE28">
-        <v>1.47</v>
-      </c>
       <c r="AF28">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="AK28">
-        <v>3.85</v>
+        <v>1.35</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-07-24 17:00:00</t>
+          <t>2026-07-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="O29">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="Q29">
+        <v>3.55</v>
+      </c>
+      <c r="R29">
+        <v>2.3</v>
+      </c>
+      <c r="S29">
+        <v>1.3</v>
+      </c>
+      <c r="T29">
         <v>3.2</v>
       </c>
-      <c r="R29">
-        <v>2</v>
-      </c>
-      <c r="S29">
-        <v>1.43</v>
-      </c>
-      <c r="T29">
-        <v>2.62</v>
-      </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>2.74</v>
+        <v>3.94</v>
       </c>
       <c r="AA29">
+        <v>1.82</v>
+      </c>
+      <c r="AB29">
         <v>2.15</v>
       </c>
-      <c r="AB29">
-        <v>1.65</v>
-      </c>
       <c r="AC29">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AD29">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-07-24 19:00:00</t>
+          <t>2026-07-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA30">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-07-24 19:00:00</t>
+          <t>2026-07-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="R31">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
         <v>2.75</v>
       </c>
       <c r="U31">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA31">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC31">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD31">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AK31">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-07-24 19:00:00</t>
+          <t>2026-07-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G32">
@@ -5521,68 +5521,68 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-07-24 20:00:00</t>
+          <t>2026-07-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.09</v>
+        <v>1.27</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="P33">
-        <v>2.83</v>
+        <v>7.7</v>
       </c>
       <c r="Q33">
-        <v>2.74</v>
+        <v>1.57</v>
       </c>
       <c r="R33">
-        <v>2.24</v>
+        <v>3.14</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="T33">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="U33">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="Z33">
-        <v>3.42</v>
+        <v>7.8</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>1.69</v>
       </c>
       <c r="AD33">
-        <v>1.32</v>
+        <v>2.11</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>1.64</v>
+        <v>3.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 17:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q34">
-        <v>4.86</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="S34">
+        <v>1.43</v>
+      </c>
+      <c r="T34">
+        <v>2.62</v>
+      </c>
+      <c r="U34">
+        <v>3.1</v>
+      </c>
+      <c r="V34">
+        <v>1.31</v>
+      </c>
+      <c r="W34">
+        <v>1.04</v>
+      </c>
+      <c r="X34">
+        <v>1.06</v>
+      </c>
+      <c r="Y34">
+        <v>1.35</v>
+      </c>
+      <c r="Z34">
+        <v>2.74</v>
+      </c>
+      <c r="AA34">
+        <v>2.15</v>
+      </c>
+      <c r="AB34">
+        <v>1.65</v>
+      </c>
+      <c r="AC34">
+        <v>3.75</v>
+      </c>
+      <c r="AD34">
         <v>1.2</v>
       </c>
-      <c r="T34">
-        <v>4</v>
-      </c>
-      <c r="U34">
-        <v>1.95</v>
-      </c>
-      <c r="V34">
-        <v>1.78</v>
-      </c>
-      <c r="W34">
-        <v>1.2</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.1</v>
-      </c>
-      <c r="Z34">
-        <v>6.31</v>
-      </c>
-      <c r="AA34">
-        <v>1.33</v>
-      </c>
-      <c r="AB34">
-        <v>2.83</v>
-      </c>
-      <c r="AC34">
-        <v>1.9</v>
-      </c>
-      <c r="AD34">
-        <v>1.8</v>
-      </c>
       <c r="AE34">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AG34">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 19:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="O35">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>6.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB35">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 19:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S36">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB36">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 19:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-07-24 21:30:00</t>
+          <t>2026-07-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.4</v>
+        <v>2.09</v>
       </c>
       <c r="O38">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>5.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q38">
-        <v>1.92</v>
+        <v>2.74</v>
       </c>
       <c r="R38">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="S38">
+        <v>1.33</v>
+      </c>
+      <c r="T38">
+        <v>2.9</v>
+      </c>
+      <c r="U38">
+        <v>2.56</v>
+      </c>
+      <c r="V38">
+        <v>1.44</v>
+      </c>
+      <c r="W38">
+        <v>1.1</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+      <c r="Y38">
+        <v>1.23</v>
+      </c>
+      <c r="Z38">
+        <v>3.59</v>
+      </c>
+      <c r="AA38">
+        <v>1.8</v>
+      </c>
+      <c r="AB38">
+        <v>1.9</v>
+      </c>
+      <c r="AC38">
+        <v>2.88</v>
+      </c>
+      <c r="AD38">
+        <v>1.32</v>
+      </c>
+      <c r="AE38">
+        <v>1.09</v>
+      </c>
+      <c r="AF38">
+        <v>1.67</v>
+      </c>
+      <c r="AG38">
+        <v>2.05</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.24</v>
       </c>
-      <c r="T38">
-        <v>3.6</v>
-      </c>
-      <c r="U38">
-        <v>2.34</v>
-      </c>
-      <c r="V38">
-        <v>1.56</v>
-      </c>
-      <c r="W38">
-        <v>1.13</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.18</v>
-      </c>
-      <c r="Z38">
-        <v>4.74</v>
-      </c>
-      <c r="AA38">
-        <v>1.6</v>
-      </c>
-      <c r="AB38">
-        <v>2.3</v>
-      </c>
-      <c r="AC38">
-        <v>2.4</v>
-      </c>
-      <c r="AD38">
-        <v>1.54</v>
-      </c>
-      <c r="AE38">
-        <v>1.17</v>
-      </c>
-      <c r="AF38">
-        <v>1.68</v>
-      </c>
-      <c r="AG38">
-        <v>2.06</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.17</v>
-      </c>
       <c r="AK38">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-07-24 21:30:00</t>
+          <t>2026-07-24 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA39">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AB39">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-07-24 23:00:00</t>
+          <t>2026-07-24 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,156 +6782,971 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Orlando Pride</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>1.35</v>
+      </c>
+      <c r="O40">
+        <v>4.75</v>
+      </c>
+      <c r="P40">
+        <v>6.65</v>
+      </c>
+      <c r="Q40">
+        <v>1.75</v>
+      </c>
+      <c r="R40">
+        <v>2.53</v>
+      </c>
+      <c r="S40">
+        <v>1.22</v>
+      </c>
+      <c r="T40">
+        <v>4</v>
+      </c>
+      <c r="U40">
+        <v>2.06</v>
+      </c>
+      <c r="V40">
+        <v>1.66</v>
+      </c>
+      <c r="W40">
+        <v>1.16</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.12</v>
+      </c>
+      <c r="Z40">
+        <v>5.1</v>
+      </c>
+      <c r="AA40">
+        <v>1.4</v>
+      </c>
+      <c r="AB40">
+        <v>2.41</v>
+      </c>
+      <c r="AC40">
+        <v>1.84</v>
+      </c>
+      <c r="AD40">
+        <v>1.64</v>
+      </c>
+      <c r="AE40">
+        <v>1.23</v>
+      </c>
+      <c r="AF40">
+        <v>1.55</v>
+      </c>
+      <c r="AG40">
+        <v>2.27</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.17</v>
+      </c>
+      <c r="AK40">
+        <v>2.4</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>2.25</v>
+      </c>
+      <c r="O41">
+        <v>3.1</v>
+      </c>
+      <c r="P41">
+        <v>2.65</v>
+      </c>
+      <c r="Q41">
+        <v>3.2</v>
+      </c>
+      <c r="R41">
+        <v>2.1</v>
+      </c>
+      <c r="S41">
+        <v>1.32</v>
+      </c>
+      <c r="T41">
+        <v>2.92</v>
+      </c>
+      <c r="U41">
+        <v>2.18</v>
+      </c>
+      <c r="V41">
+        <v>1.35</v>
+      </c>
+      <c r="W41">
+        <v>1.05</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>1.2</v>
+      </c>
+      <c r="Z41">
+        <v>3.42</v>
+      </c>
+      <c r="AA41">
+        <v>1.83</v>
+      </c>
+      <c r="AB41">
+        <v>1.82</v>
+      </c>
+      <c r="AC41">
+        <v>2.5</v>
+      </c>
+      <c r="AD41">
+        <v>1.28</v>
+      </c>
+      <c r="AE41">
+        <v>1.07</v>
+      </c>
+      <c r="AF41">
+        <v>1.65</v>
+      </c>
+      <c r="AG41">
+        <v>1.85</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.44</v>
+      </c>
+      <c r="AK41">
+        <v>1.39</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>1.4</v>
+      </c>
+      <c r="O43">
+        <v>4.45</v>
+      </c>
+      <c r="P43">
+        <v>5.5</v>
+      </c>
+      <c r="Q43">
+        <v>1.92</v>
+      </c>
+      <c r="R43">
+        <v>2.63</v>
+      </c>
+      <c r="S43">
+        <v>1.24</v>
+      </c>
+      <c r="T43">
+        <v>3.6</v>
+      </c>
+      <c r="U43">
+        <v>2.34</v>
+      </c>
+      <c r="V43">
+        <v>1.56</v>
+      </c>
+      <c r="W43">
+        <v>1.13</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.18</v>
+      </c>
+      <c r="Z43">
+        <v>4.74</v>
+      </c>
+      <c r="AA43">
+        <v>1.6</v>
+      </c>
+      <c r="AB43">
+        <v>2.3</v>
+      </c>
+      <c r="AC43">
+        <v>2.4</v>
+      </c>
+      <c r="AD43">
+        <v>1.54</v>
+      </c>
+      <c r="AE43">
+        <v>1.17</v>
+      </c>
+      <c r="AF43">
+        <v>1.68</v>
+      </c>
+      <c r="AG43">
+        <v>2.06</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.17</v>
+      </c>
+      <c r="AK43">
+        <v>2.7</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>3.29</v>
+      </c>
+      <c r="O44">
+        <v>3.22</v>
+      </c>
+      <c r="P44">
+        <v>2.06</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>1.95</v>
+      </c>
+      <c r="AB44">
+        <v>1.85</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-07-24 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Portland Thorns</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Gotham FC</t>
         </is>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>0</v>
-      </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
-      </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
-      <c r="AF40">
-        <v>0</v>
-      </c>
-      <c r="AG40">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
-      <c r="AK40">
-        <v>0</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>-1</v>
-      </c>
-      <c r="AN40">
-        <v>-1</v>
-      </c>
-      <c r="AO40">
-        <v>-1</v>
-      </c>
-      <c r="AP40">
-        <v>-1</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
-      <c r="AS40">
-        <v>0</v>
-      </c>
-      <c r="AT40">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>2026-07-24 23:00:00</t>
         </is>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="O2">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
         <v>1.28</v>
@@ -656,28 +656,28 @@
         <v>3.14</v>
       </c>
       <c r="U2">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z2">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA2">
         <v>1.67</v>
       </c>
       <c r="AB2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC2">
         <v>2.66</v>
@@ -686,7 +686,7 @@
         <v>1.37</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
         <v>1.56</v>
@@ -801,16 +801,16 @@
         <v>2.7</v>
       </c>
       <c r="O3">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="S3">
         <v>1.42</v>
@@ -819,16 +819,16 @@
         <v>2.56</v>
       </c>
       <c r="U3">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.33</v>
@@ -840,7 +840,7 @@
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
         <v>3.58</v>
@@ -849,10 +849,10 @@
         <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
         <v>1.86</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AK3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
         <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -997,7 +997,7 @@
         <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="AA4">
         <v>1.62</v>
@@ -1009,7 +1009,7 @@
         <v>2.48</v>
       </c>
       <c r="AD4">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
         <v>1.14</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="O8">
         <v>3.3</v>
       </c>
       <c r="P8">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P10">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q10">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
+        <v>2.4</v>
+      </c>
+      <c r="S10">
+        <v>1.27</v>
+      </c>
+      <c r="T10">
+        <v>3.2</v>
+      </c>
+      <c r="U10">
+        <v>2.41</v>
+      </c>
+      <c r="V10">
+        <v>1.46</v>
+      </c>
+      <c r="W10">
+        <v>1.12</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.2</v>
+      </c>
+      <c r="Z10">
+        <v>4.1</v>
+      </c>
+      <c r="AA10">
+        <v>1.66</v>
+      </c>
+      <c r="AB10">
         <v>2.15</v>
       </c>
-      <c r="S10">
-        <v>1.32</v>
-      </c>
-      <c r="T10">
-        <v>3.1</v>
-      </c>
-      <c r="U10">
-        <v>2.56</v>
-      </c>
-      <c r="V10">
-        <v>1.41</v>
-      </c>
-      <c r="W10">
-        <v>1.06</v>
-      </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
-        <v>1.21</v>
-      </c>
-      <c r="Z10">
-        <v>3.58</v>
-      </c>
-      <c r="AA10">
-        <v>1.8</v>
-      </c>
-      <c r="AB10">
-        <v>1.94</v>
-      </c>
       <c r="AC10">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.83</v>
+        <v>2.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>5.25</v>
+        <v>2.87</v>
       </c>
       <c r="Q11">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="O12">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>5.23</v>
+        <v>3.75</v>
       </c>
       <c r="Q12">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
         <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -2304,13 +2304,13 @@
         <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC12">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD12">
         <v>1.33</v>
@@ -2319,10 +2319,10 @@
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,65 +2428,65 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13">
-        <v>2.98</v>
+        <v>2.12</v>
       </c>
       <c r="R13">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z13">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA13">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
+        <v>2</v>
+      </c>
+      <c r="AC13">
+        <v>2.81</v>
+      </c>
+      <c r="AD13">
+        <v>1.33</v>
+      </c>
+      <c r="AE13">
+        <v>1.09</v>
+      </c>
+      <c r="AF13">
+        <v>1.73</v>
+      </c>
+      <c r="AG13">
         <v>1.9</v>
       </c>
-      <c r="AC13">
-        <v>2.97</v>
-      </c>
-      <c r="AD13">
-        <v>1.3</v>
-      </c>
-      <c r="AE13">
-        <v>1.08</v>
-      </c>
-      <c r="AF13">
-        <v>1.62</v>
-      </c>
-      <c r="AG13">
-        <v>2.2</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="U14">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="V14">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="O15">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P15">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="Q15">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S15">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
         <v>2.23</v>
@@ -2781,22 +2781,22 @@
         <v>1.61</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>5.05</v>
+        <v>4.3</v>
       </c>
       <c r="AA15">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB15">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AC15">
         <v>2.29</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>1.59</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z19">
-        <v>4.93</v>
+        <v>6.5</v>
       </c>
       <c r="AA19">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AC19">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="AD19">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AF19">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>2.24</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.59</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>3.36</v>
       </c>
       <c r="R20">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="V20">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>6.5</v>
+        <v>4.93</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AB20">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC20">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="AD20">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AE20">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AF20">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG20">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AK20">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.11</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>2.97</v>
+        <v>1.51</v>
       </c>
       <c r="Q22">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T22">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>5.06</v>
+        <v>5.35</v>
       </c>
       <c r="AA22">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AC22">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AD22">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF22">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AG22">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK22">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.6</v>
+        <v>2.11</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P23">
-        <v>1.51</v>
+        <v>2.97</v>
       </c>
       <c r="Q23">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="T23">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="U23">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>5.35</v>
+        <v>5.06</v>
       </c>
       <c r="AA23">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AB23">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AC23">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AD23">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE23">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG23">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="O33">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P33">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="Q33">
         <v>1.57</v>
       </c>
       <c r="R33">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="S33">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="T33">
         <v>4.8</v>
@@ -5715,7 +5715,7 @@
         <v>1.97</v>
       </c>
       <c r="W33">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5724,13 +5724,13 @@
         <v>1.02</v>
       </c>
       <c r="Z33">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AB33">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AC33">
         <v>1.69</v>
@@ -5739,13 +5739,13 @@
         <v>2.11</v>
       </c>
       <c r="AE33">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK33">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="Q34">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S34">
         <v>1.43</v>
@@ -5872,22 +5872,22 @@
         <v>2.62</v>
       </c>
       <c r="U34">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="V34">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
         <v>1.04</v>
       </c>
-      <c r="X34">
-        <v>1.06</v>
-      </c>
       <c r="Y34">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z34">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA34">
         <v>2.15</v>
@@ -5896,19 +5896,19 @@
         <v>1.65</v>
       </c>
       <c r="AC34">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD34">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE34">
         <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG34">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA35">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB35">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6216,7 +6216,7 @@
         <v>3.2</v>
       </c>
       <c r="AA36">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB36">
         <v>1.8</v>
@@ -6841,19 +6841,19 @@
         <v>1.75</v>
       </c>
       <c r="R40">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
         <v>4</v>
       </c>
       <c r="U40">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="V40">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
         <v>1.16</v>
@@ -6868,16 +6868,16 @@
         <v>5.1</v>
       </c>
       <c r="AA40">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB40">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AC40">
         <v>1.84</v>
       </c>
       <c r="AD40">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AE40">
         <v>1.23</v>
@@ -6886,7 +6886,7 @@
         <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>2.65</v>
       </c>
       <c r="Q41">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S41">
         <v>1.32</v>
@@ -7013,19 +7013,19 @@
         <v>2.92</v>
       </c>
       <c r="U41">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
         <v>3.42</v>
@@ -7037,16 +7037,16 @@
         <v>1.82</v>
       </c>
       <c r="AC41">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD41">
         <v>1.28</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
         <v>1.85</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
         <v>1.39</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O43">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P43">
         <v>5.5</v>
@@ -7330,19 +7330,19 @@
         <v>1.92</v>
       </c>
       <c r="R43">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
         <v>3.6</v>
       </c>
       <c r="U43">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="V43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
         <v>1.13</v>
@@ -7354,19 +7354,19 @@
         <v>1.18</v>
       </c>
       <c r="Z43">
-        <v>4.74</v>
+        <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC43">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD43">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE43">
         <v>1.17</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK43">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU45"/>
+  <dimension ref="A1:AU44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O6">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
         <v>3.5</v>
@@ -1335,7 +1335,7 @@
         <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
         <v>1.06</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O7">
         <v>3.5</v>
@@ -1459,22 +1459,22 @@
         <v>3.76</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
         <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
         <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
         <v>1.12</v>
@@ -1489,10 +1489,10 @@
         <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC7">
         <v>2.7</v>
@@ -1504,7 +1504,7 @@
         <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG7">
         <v>2.2</v>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="Q11">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC11">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="P12">
-        <v>3.75</v>
+        <v>5.23</v>
       </c>
       <c r="Q12">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="R12">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
         <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -2304,13 +2304,13 @@
         <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD12">
         <v>1.33</v>
@@ -2319,10 +2319,10 @@
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>5.23</v>
+        <v>2.87</v>
       </c>
       <c r="Q13">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>1.17</v>
+      </c>
+      <c r="Z13">
+        <v>4</v>
+      </c>
+      <c r="AA13">
+        <v>1.7</v>
+      </c>
+      <c r="AB13">
+        <v>2.05</v>
+      </c>
+      <c r="AC13">
+        <v>2.62</v>
+      </c>
+      <c r="AD13">
+        <v>1.38</v>
+      </c>
+      <c r="AE13">
         <v>1.11</v>
       </c>
-      <c r="X13">
-        <v>1</v>
-      </c>
-      <c r="Y13">
-        <v>1.21</v>
-      </c>
-      <c r="Z13">
-        <v>3.58</v>
-      </c>
-      <c r="AA13">
-        <v>1.75</v>
-      </c>
-      <c r="AB13">
-        <v>2</v>
-      </c>
-      <c r="AC13">
-        <v>2.81</v>
-      </c>
-      <c r="AD13">
-        <v>1.33</v>
-      </c>
-      <c r="AE13">
-        <v>1.09</v>
-      </c>
       <c r="AF13">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -4553,28 +4553,28 @@
         <v>3</v>
       </c>
       <c r="P26">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="Q26">
         <v>2.9</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U26">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
         <v>1.04</v>
@@ -4583,28 +4583,28 @@
         <v>1.5</v>
       </c>
       <c r="Z26">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AA26">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AB26">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AC26">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
       <c r="AD26">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE26">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
         <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK26">
         <v>1.64</v>
@@ -5377,13 +5377,13 @@
         <v>2.08</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T31">
+        <v>3.08</v>
+      </c>
+      <c r="U31">
         <v>2.75</v>
-      </c>
-      <c r="U31">
-        <v>2.62</v>
       </c>
       <c r="V31">
         <v>1.4</v>
@@ -5691,13 +5691,13 @@
         <v>1.23</v>
       </c>
       <c r="O33">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="P33">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="Q33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R33">
         <v>3.26</v>
@@ -5724,7 +5724,7 @@
         <v>1.02</v>
       </c>
       <c r="Z33">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="AA33">
         <v>1.24</v>
@@ -5742,7 +5742,7 @@
         <v>1.44</v>
       </c>
       <c r="AF33">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
         <v>2.34</v>
@@ -5761,7 +5761,7 @@
         <v>1.03</v>
       </c>
       <c r="AK33">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="R34">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="U34">
-        <v>3.21</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="AA34">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AC34">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD34">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
         <v>3.6</v>
       </c>
-      <c r="P35">
-        <v>3.4</v>
-      </c>
-      <c r="Q35">
-        <v>2.37</v>
-      </c>
       <c r="R35">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA35">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB35">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36">
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-07-24 19:00:00</t>
+          <t>2026-07-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-07-24 20:00:00</t>
+          <t>2026-07-24 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="R38">
-        <v>2.14</v>
+        <v>2.65</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="T38">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="U38">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="W38">
+        <v>1.2</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.07</v>
+      </c>
+      <c r="Z38">
+        <v>5.9</v>
+      </c>
+      <c r="AA38">
+        <v>1.36</v>
+      </c>
+      <c r="AB38">
+        <v>3.1</v>
+      </c>
+      <c r="AC38">
+        <v>1.9</v>
+      </c>
+      <c r="AD38">
+        <v>1.8</v>
+      </c>
+      <c r="AE38">
+        <v>1.34</v>
+      </c>
+      <c r="AF38">
+        <v>1.45</v>
+      </c>
+      <c r="AG38">
+        <v>2.5</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>1.12</v>
+      </c>
+      <c r="AK38">
         <v>1.1</v>
-      </c>
-      <c r="X38">
-        <v>1</v>
-      </c>
-      <c r="Y38">
-        <v>1.23</v>
-      </c>
-      <c r="Z38">
-        <v>3.59</v>
-      </c>
-      <c r="AA38">
-        <v>1.8</v>
-      </c>
-      <c r="AB38">
-        <v>1.9</v>
-      </c>
-      <c r="AC38">
-        <v>2.88</v>
-      </c>
-      <c r="AD38">
-        <v>1.32</v>
-      </c>
-      <c r="AE38">
-        <v>1.09</v>
-      </c>
-      <c r="AF38">
-        <v>1.67</v>
-      </c>
-      <c r="AG38">
-        <v>2.05</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.24</v>
-      </c>
-      <c r="AK38">
-        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q39">
-        <v>4.75</v>
+        <v>1.75</v>
       </c>
       <c r="R39">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
+        <v>1.2</v>
+      </c>
+      <c r="T39">
+        <v>4</v>
+      </c>
+      <c r="U39">
+        <v>2.01</v>
+      </c>
+      <c r="V39">
+        <v>1.65</v>
+      </c>
+      <c r="W39">
         <v>1.16</v>
       </c>
-      <c r="T39">
-        <v>4.6</v>
-      </c>
-      <c r="U39">
-        <v>2</v>
-      </c>
-      <c r="V39">
-        <v>1.78</v>
-      </c>
-      <c r="W39">
-        <v>1.2</v>
-      </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB39">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AC39">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AD39">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AE39">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AF39">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG39">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK39">
-        <v>1.1</v>
+        <v>2.43</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>6.65</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="R40">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="U40">
-        <v>2.01</v>
+        <v>2.63</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="W40">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>5.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA40">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AB40">
-        <v>2.56</v>
+        <v>1.82</v>
       </c>
       <c r="AC40">
-        <v>1.84</v>
+        <v>3.08</v>
       </c>
       <c r="AD40">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="AE40">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>2.43</v>
+        <v>1.39</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-07-24 21:00:00</t>
+          <t>2026-07-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.45</v>
+        <v>3.29</v>
       </c>
       <c r="O43">
-        <v>4.2</v>
+        <v>3.22</v>
       </c>
       <c r="P43">
-        <v>5.5</v>
+        <v>2.06</v>
       </c>
       <c r="Q43">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC43">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-07-24 21:30:00</t>
+          <t>2026-07-24 23:00:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7584,169 +7584,6 @@
         <v>0</v>
       </c>
       <c r="AU44" t="inlineStr">
-        <is>
-          <t>2026-07-24 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>0</v>
-      </c>
-      <c r="Y45">
-        <v>0</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45">
-        <v>0</v>
-      </c>
-      <c r="AB45">
-        <v>0</v>
-      </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AD45">
-        <v>0</v>
-      </c>
-      <c r="AE45">
-        <v>0</v>
-      </c>
-      <c r="AF45">
-        <v>0</v>
-      </c>
-      <c r="AG45">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>0</v>
-      </c>
-      <c r="AK45">
-        <v>0</v>
-      </c>
-      <c r="AL45">
-        <v>0</v>
-      </c>
-      <c r="AM45">
-        <v>-1</v>
-      </c>
-      <c r="AN45">
-        <v>-1</v>
-      </c>
-      <c r="AO45">
-        <v>-1</v>
-      </c>
-      <c r="AP45">
-        <v>-1</v>
-      </c>
-      <c r="AQ45">
-        <v>0</v>
-      </c>
-      <c r="AR45">
-        <v>0</v>
-      </c>
-      <c r="AS45">
-        <v>0</v>
-      </c>
-      <c r="AT45">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
         <is>
           <t>2026-07-24 23:00:00</t>
         </is>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P2">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R2">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S2">
         <v>1.28</v>
@@ -656,43 +656,43 @@
         <v>3.14</v>
       </c>
       <c r="U2">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB2">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
         <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG2">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,22 +1290,22 @@
         <v>2.05</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="R6">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U6">
         <v>2.9</v>
@@ -1314,28 +1314,28 @@
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
         <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC6">
         <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
         <v>1.06</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
         <v>1.58</v>
@@ -1450,43 +1450,43 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O7">
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="Q7">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="U7">
         <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA7">
         <v>1.66</v>
@@ -1495,10 +1495,10 @@
         <v>2.14</v>
       </c>
       <c r="AC7">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AD7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE7">
         <v>1.13</v>
@@ -1507,7 +1507,7 @@
         <v>1.56</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O8">
         <v>3.3</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
+        <v>1.95</v>
+      </c>
+      <c r="AB8">
         <v>1.85</v>
-      </c>
-      <c r="AB8">
-        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="O9">
         <v>3.28</v>
@@ -1785,25 +1785,25 @@
         <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R9">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U9">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="V9">
         <v>1.45</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1818,10 +1818,10 @@
         <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD9">
         <v>1.42</v>
@@ -1830,10 +1830,10 @@
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AG9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,16 +1942,16 @@
         <v>1.48</v>
       </c>
       <c r="O10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
         <v>5.25</v>
       </c>
       <c r="Q10">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="R10">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S10">
         <v>1.27</v>
@@ -1966,25 +1966,25 @@
         <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
         <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
         <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AD10">
         <v>1.39</v>
@@ -1993,10 +1993,10 @@
         <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P11">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="Q11">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
         <v>2.56</v>
@@ -2132,7 +2132,7 @@
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.21</v>
@@ -2141,19 +2141,19 @@
         <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB11">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AC11">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.65</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,31 +2268,31 @@
         <v>1.57</v>
       </c>
       <c r="O12">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>5.23</v>
+        <v>4.6</v>
       </c>
       <c r="Q12">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
         <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -2304,10 +2304,10 @@
         <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC12">
         <v>2.81</v>
@@ -2319,7 +2319,7 @@
         <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG12">
         <v>1.9</v>
@@ -2338,7 +2338,7 @@
         <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="Q13">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U13">
         <v>2.49</v>
@@ -2467,10 +2467,10 @@
         <v>4</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
         <v>2.62</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="R14">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
         <v>2.79</v>
       </c>
       <c r="U14">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="V14">
         <v>1.38</v>
@@ -2621,7 +2621,7 @@
         <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.25</v>
@@ -2630,25 +2630,25 @@
         <v>3.42</v>
       </c>
       <c r="AA14">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
+        <v>1.24</v>
+      </c>
+      <c r="AK14">
         <v>1.44</v>
-      </c>
-      <c r="AK14">
-        <v>1.45</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O15">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="Q15">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U15">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V15">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z15">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
         <v>2.39</v>
       </c>
       <c r="AC15">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF15">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,13 +2923,13 @@
         <v>3.2</v>
       </c>
       <c r="P16">
-        <v>4.06</v>
+        <v>3.25</v>
       </c>
       <c r="Q16">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="R16">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="S16">
         <v>1.51</v>
@@ -2950,22 +2950,22 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z16">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="AB16">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AD16">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
         <v>1.03</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,46 +3083,46 @@
         <v>1.85</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="P17">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q17">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
         <v>4.4</v>
       </c>
       <c r="AA17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB17">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC17">
         <v>2.63</v>
@@ -3131,7 +3131,7 @@
         <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
         <v>1.57</v>
@@ -3153,7 +3153,7 @@
         <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="O18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="R18">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="S18">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T18">
         <v>5.2</v>
       </c>
       <c r="U18">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V18">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="W18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,29 +3279,29 @@
         <v>1.05</v>
       </c>
       <c r="Z18">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB18">
+        <v>3.25</v>
+      </c>
+      <c r="AC18">
+        <v>1.83</v>
+      </c>
+      <c r="AD18">
+        <v>1.87</v>
+      </c>
+      <c r="AE18">
+        <v>1.35</v>
+      </c>
+      <c r="AF18">
+        <v>1.33</v>
+      </c>
+      <c r="AG18">
         <v>3</v>
       </c>
-      <c r="AC18">
-        <v>1.81</v>
-      </c>
-      <c r="AD18">
-        <v>1.94</v>
-      </c>
-      <c r="AE18">
-        <v>1.36</v>
-      </c>
-      <c r="AF18">
-        <v>1.36</v>
-      </c>
-      <c r="AG18">
-        <v>2.79</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK18">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.59</v>
+        <v>2.69</v>
       </c>
       <c r="O19">
+        <v>3.4</v>
+      </c>
+      <c r="P19">
+        <v>2.21</v>
+      </c>
+      <c r="Q19">
+        <v>3.36</v>
+      </c>
+      <c r="R19">
+        <v>2.27</v>
+      </c>
+      <c r="S19">
+        <v>1.26</v>
+      </c>
+      <c r="T19">
+        <v>3.2</v>
+      </c>
+      <c r="U19">
+        <v>2.28</v>
+      </c>
+      <c r="V19">
+        <v>1.55</v>
+      </c>
+      <c r="W19">
+        <v>1.11</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>1.14</v>
+      </c>
+      <c r="Z19">
         <v>4.4</v>
       </c>
-      <c r="P19">
-        <v>4.1</v>
-      </c>
-      <c r="Q19">
-        <v>2</v>
-      </c>
-      <c r="R19">
-        <v>2.54</v>
-      </c>
-      <c r="S19">
+      <c r="AA19">
+        <v>1.56</v>
+      </c>
+      <c r="AB19">
+        <v>2.35</v>
+      </c>
+      <c r="AC19">
+        <v>2.33</v>
+      </c>
+      <c r="AD19">
+        <v>1.48</v>
+      </c>
+      <c r="AE19">
         <v>1.17</v>
       </c>
-      <c r="T19">
-        <v>4</v>
-      </c>
-      <c r="U19">
-        <v>2</v>
-      </c>
-      <c r="V19">
-        <v>1.73</v>
-      </c>
-      <c r="W19">
-        <v>1.15</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.08</v>
-      </c>
-      <c r="Z19">
-        <v>6.5</v>
-      </c>
-      <c r="AA19">
-        <v>1.44</v>
-      </c>
-      <c r="AB19">
-        <v>2.8</v>
-      </c>
-      <c r="AC19">
-        <v>1.98</v>
-      </c>
-      <c r="AD19">
-        <v>1.74</v>
-      </c>
-      <c r="AE19">
-        <v>1.31</v>
-      </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG19">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>5.42</v>
       </c>
       <c r="Q20">
-        <v>3.36</v>
+        <v>1.9</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="U20">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>4.93</v>
+        <v>6.25</v>
       </c>
       <c r="AA20">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB20">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AC20">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="AD20">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AE20">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG20">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O21">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U21">
         <v>2.38</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
         <v>1.19</v>
       </c>
       <c r="Z21">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>4.49</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P22">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="Q22">
-        <v>4.75</v>
+        <v>4.36</v>
       </c>
       <c r="R22">
         <v>2.5</v>
       </c>
       <c r="S22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V22">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="AA22">
         <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AC22">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD22">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE22">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG22">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.14</v>
+        <v>2.01</v>
       </c>
       <c r="AK22">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
         <v>2.97</v>
       </c>
       <c r="Q23">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S23">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T23">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U23">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>5.06</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB23">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AC23">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD23">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AG23">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="U24">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="AA24">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE24">
         <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG24">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="P25">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R25">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U25">
         <v>2.95</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AA25">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC25">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD25">
         <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG25">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,34 +4556,34 @@
         <v>3.3</v>
       </c>
       <c r="Q26">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="R26">
         <v>1.88</v>
       </c>
       <c r="S26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T26">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U26">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="V26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W26">
         <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y26">
         <v>1.5</v>
       </c>
       <c r="Z26">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AA26">
         <v>2.5</v>
@@ -4598,13 +4598,13 @@
         <v>1.17</v>
       </c>
       <c r="AE26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG26">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
         <v>1.64</v>
@@ -4719,55 +4719,55 @@
         <v>4.2</v>
       </c>
       <c r="Q27">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB27">
         <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG27">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="O28">
         <v>3.2</v>
       </c>
       <c r="P28">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
         <v>2.7</v>
       </c>
       <c r="U28">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z28">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB28">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC28">
         <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
         <v>1.68</v>
       </c>
       <c r="AG28">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,58 +5036,58 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="AA29">
         <v>1.82</v>
       </c>
       <c r="AB29">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC29">
         <v>3</v>
       </c>
       <c r="AD29">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
         <v>1.66</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5205,55 +5205,55 @@
         <v>3.3</v>
       </c>
       <c r="P30">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q30">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="R30">
+        <v>2.35</v>
+      </c>
+      <c r="S30">
+        <v>1.3</v>
+      </c>
+      <c r="T30">
+        <v>3.08</v>
+      </c>
+      <c r="U30">
         <v>2.2</v>
       </c>
-      <c r="S30">
-        <v>1.29</v>
-      </c>
-      <c r="T30">
-        <v>3.25</v>
-      </c>
-      <c r="U30">
-        <v>2.5</v>
-      </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
         <v>4.15</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB30">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AC30">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AG30">
         <v>2.34</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O31">
         <v>3.25</v>
@@ -5371,28 +5371,28 @@
         <v>2</v>
       </c>
       <c r="Q31">
-        <v>3.52</v>
+        <v>3.94</v>
       </c>
       <c r="R31">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
         <v>1.34</v>
       </c>
       <c r="T31">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V31">
         <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.23</v>
@@ -5401,13 +5401,13 @@
         <v>3.42</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD31">
         <v>1.3</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
         <v>1.27</v>
@@ -5528,28 +5528,28 @@
         <v>1.55</v>
       </c>
       <c r="O32">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P32">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="Q32">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5558,47 +5558,47 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
+        <v>1.16</v>
+      </c>
+      <c r="Z32">
+        <v>4.1</v>
+      </c>
+      <c r="AA32">
+        <v>1.6</v>
+      </c>
+      <c r="AB32">
+        <v>2.14</v>
+      </c>
+      <c r="AC32">
+        <v>2.55</v>
+      </c>
+      <c r="AD32">
+        <v>1.43</v>
+      </c>
+      <c r="AE32">
+        <v>1.15</v>
+      </c>
+      <c r="AF32">
+        <v>1.66</v>
+      </c>
+      <c r="AG32">
+        <v>2.02</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.18</v>
       </c>
-      <c r="Z32">
-        <v>3.88</v>
-      </c>
-      <c r="AA32">
-        <v>1.66</v>
-      </c>
-      <c r="AB32">
-        <v>2.15</v>
-      </c>
-      <c r="AC32">
-        <v>2.87</v>
-      </c>
-      <c r="AD32">
-        <v>1.39</v>
-      </c>
-      <c r="AE32">
-        <v>1.11</v>
-      </c>
-      <c r="AF32">
-        <v>1.64</v>
-      </c>
-      <c r="AG32">
-        <v>2.01</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.21</v>
-      </c>
       <c r="AK32">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="O33">
         <v>6.6</v>
@@ -5697,16 +5697,16 @@
         <v>8.5</v>
       </c>
       <c r="Q33">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R33">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="S33">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="T33">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="U33">
         <v>1.77</v>
@@ -5721,31 +5721,31 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z33">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AB33">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AC33">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AD33">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AE33">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF33">
         <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="R34">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="U34">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
+        <v>1.1</v>
+      </c>
+      <c r="X34">
+        <v>1.03</v>
+      </c>
+      <c r="Y34">
+        <v>1.17</v>
+      </c>
+      <c r="Z34">
+        <v>3.98</v>
+      </c>
+      <c r="AA34">
+        <v>1.7</v>
+      </c>
+      <c r="AB34">
+        <v>2.1</v>
+      </c>
+      <c r="AC34">
+        <v>2.66</v>
+      </c>
+      <c r="AD34">
+        <v>1.37</v>
+      </c>
+      <c r="AE34">
         <v>1.11</v>
       </c>
-      <c r="X34">
-        <v>1.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.16</v>
-      </c>
-      <c r="Z34">
-        <v>4.15</v>
-      </c>
-      <c r="AA34">
-        <v>1.65</v>
-      </c>
-      <c r="AB34">
-        <v>2.08</v>
-      </c>
-      <c r="AC34">
-        <v>2.56</v>
-      </c>
-      <c r="AD34">
-        <v>1.4</v>
-      </c>
-      <c r="AE34">
-        <v>1.12</v>
-      </c>
       <c r="AF34">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,19 +6023,19 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R35">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S35">
         <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
         <v>1.36</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="Q37">
         <v>2.65</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S37">
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -6379,25 +6379,25 @@
         <v>4.17</v>
       </c>
       <c r="AA37">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="R38">
         <v>2.65</v>
@@ -6524,13 +6524,13 @@
         <v>4.6</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V38">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X38">
         <v>1.01</v>
@@ -6542,10 +6542,10 @@
         <v>5.9</v>
       </c>
       <c r="AA38">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB38">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AC38">
         <v>1.9</v>
@@ -6554,13 +6554,13 @@
         <v>1.8</v>
       </c>
       <c r="AE38">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AF38">
         <v>1.45</v>
       </c>
       <c r="AG38">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="O39">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="P39">
-        <v>6.65</v>
+        <v>4.4</v>
       </c>
       <c r="Q39">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="R39">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U39">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="V39">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W39">
         <v>1.16</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y39">
         <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA39">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC39">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AD39">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AE39">
         <v>1.23</v>
       </c>
       <c r="AF39">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK39">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="Q40">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S40">
         <v>1.32</v>
@@ -6862,19 +6862,19 @@
         <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB40">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD40">
         <v>1.28</v>
@@ -6886,7 +6886,7 @@
         <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.29</v>
+        <v>2.87</v>
       </c>
       <c r="O43">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
+        <v>1.85</v>
+      </c>
+      <c r="AB43">
         <v>1.95</v>
-      </c>
-      <c r="AB43">
-        <v>1.85</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3">
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.93</v>
       </c>
       <c r="P3">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q3">
-        <v>3.55</v>
+        <v>2.02</v>
       </c>
       <c r="R3">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="U3">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="AA3">
+        <v>1.66</v>
+      </c>
+      <c r="AB3">
+        <v>2.15</v>
+      </c>
+      <c r="AC3">
+        <v>2.48</v>
+      </c>
+      <c r="AD3">
+        <v>1.41</v>
+      </c>
+      <c r="AE3">
+        <v>1.14</v>
+      </c>
+      <c r="AF3">
+        <v>1.68</v>
+      </c>
+      <c r="AG3">
         <v>2.1</v>
       </c>
-      <c r="AB3">
-        <v>1.67</v>
-      </c>
-      <c r="AC3">
-        <v>3.58</v>
-      </c>
-      <c r="AD3">
-        <v>1.25</v>
-      </c>
-      <c r="AE3">
-        <v>1.04</v>
-      </c>
-      <c r="AF3">
-        <v>1.8</v>
-      </c>
-      <c r="AG3">
-        <v>1.86</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="AK3">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>3.94</v>
       </c>
       <c r="R4">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="V4">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z4">
-        <v>4.26</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>2.2</v>
+        <v>1.28</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,34 +7155,34 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O42">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P42">
         <v>5.5</v>
       </c>
       <c r="Q42">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T42">
         <v>3.6</v>
       </c>
       <c r="U42">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="V42">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.01</v>
@@ -7191,19 +7191,19 @@
         <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA42">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB42">
         <v>2.35</v>
       </c>
       <c r="AC42">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD42">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE42">
         <v>1.17</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
         <v>2.61</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.42</v>
+        <v>2.7</v>
       </c>
       <c r="O3">
-        <v>3.93</v>
+        <v>3.05</v>
       </c>
       <c r="P3">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
+        <v>3.94</v>
+      </c>
+      <c r="R3">
         <v>2.02</v>
       </c>
-      <c r="R3">
-        <v>2.38</v>
-      </c>
       <c r="S3">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
-        <v>3.32</v>
+        <v>2.59</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="V3">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AK3">
-        <v>2.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="O4">
-        <v>3.05</v>
+        <v>3.93</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>3.94</v>
+        <v>2.02</v>
       </c>
       <c r="R4">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="T4">
-        <v>2.59</v>
+        <v>3.32</v>
       </c>
       <c r="U4">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
+        <v>1.66</v>
+      </c>
+      <c r="AB4">
+        <v>2.15</v>
+      </c>
+      <c r="AC4">
+        <v>2.48</v>
+      </c>
+      <c r="AD4">
+        <v>1.41</v>
+      </c>
+      <c r="AE4">
+        <v>1.14</v>
+      </c>
+      <c r="AF4">
+        <v>1.68</v>
+      </c>
+      <c r="AG4">
         <v>2.1</v>
       </c>
-      <c r="AB4">
-        <v>1.7</v>
-      </c>
-      <c r="AC4">
-        <v>3.5</v>
-      </c>
-      <c r="AD4">
-        <v>1.26</v>
-      </c>
-      <c r="AE4">
-        <v>1.04</v>
-      </c>
-      <c r="AF4">
-        <v>1.8</v>
-      </c>
-      <c r="AG4">
-        <v>1.87</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>1.28</v>
+        <v>2.29</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         <v>2.05</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q6">
         <v>2.69</v>
@@ -1305,7 +1305,7 @@
         <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
         <v>2.9</v>
@@ -1320,16 +1320,16 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
         <v>3.34</v>
@@ -1344,7 +1344,7 @@
         <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2920,13 +2920,13 @@
         <v>1.99</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="P16">
-        <v>3.25</v>
+        <v>4.16</v>
       </c>
       <c r="Q16">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="R16">
         <v>1.93</v>
@@ -2956,7 +2956,7 @@
         <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB16">
         <v>1.75</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AK16">
         <v>1.83</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.65</v>
+        <v>2.69</v>
       </c>
       <c r="O18">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.8</v>
+        <v>2.21</v>
       </c>
       <c r="Q18">
-        <v>2.17</v>
+        <v>3.36</v>
       </c>
       <c r="R18">
-        <v>2.74</v>
+        <v>2.27</v>
       </c>
       <c r="S18">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="T18">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA18">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AB18">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AD18">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="AE18">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AG18">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.69</v>
+        <v>1.5</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P19">
-        <v>2.21</v>
+        <v>5.42</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>1.9</v>
       </c>
       <c r="R19">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="S19">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="V19">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="AA19">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AC19">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="AD19">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AE19">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG19">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="O20">
         <v>4.2</v>
       </c>
       <c r="P20">
-        <v>5.42</v>
+        <v>3.8</v>
       </c>
       <c r="Q20">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="R20">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="S20">
         <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="U20">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="V20">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AC20">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AD20">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF20">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4577,10 +4577,10 @@
         <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z26">
         <v>2.53</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -6340,55 +6340,55 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="P37">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
         <v>1.47</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="AA37">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC37">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
         <v>1.12</v>
@@ -6397,7 +6397,7 @@
         <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O2">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q2">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S2">
         <v>1.28</v>
       </c>
       <c r="T2">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="U2">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA2">
         <v>1.7</v>
       </c>
       <c r="AB2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC2">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
         <v>1.58</v>
       </c>
       <c r="AG2">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK2">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3">
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="O3">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q3">
-        <v>3.94</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.59</v>
+        <v>3.32</v>
       </c>
       <c r="U3">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>2.88</v>
+        <v>4.42</v>
       </c>
       <c r="AA3">
+        <v>1.66</v>
+      </c>
+      <c r="AB3">
+        <v>2.15</v>
+      </c>
+      <c r="AC3">
+        <v>2.52</v>
+      </c>
+      <c r="AD3">
+        <v>1.41</v>
+      </c>
+      <c r="AE3">
+        <v>1.14</v>
+      </c>
+      <c r="AF3">
+        <v>1.67</v>
+      </c>
+      <c r="AG3">
         <v>2.1</v>
       </c>
-      <c r="AB3">
-        <v>1.7</v>
-      </c>
-      <c r="AC3">
-        <v>3.5</v>
-      </c>
-      <c r="AD3">
-        <v>1.26</v>
-      </c>
-      <c r="AE3">
-        <v>1.04</v>
-      </c>
-      <c r="AF3">
-        <v>1.8</v>
-      </c>
-      <c r="AG3">
-        <v>1.87</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AK3">
-        <v>1.28</v>
+        <v>2.38</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.42</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>3.93</v>
+        <v>3.05</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>3.34</v>
       </c>
       <c r="R4">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.36</v>
+        <v>2.91</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA4">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>2.48</v>
+        <v>3.8</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>2.29</v>
+        <v>1.29</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,61 +1127,61 @@
         <v>1.9</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P5">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="Q5">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="R5">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AA5">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
         <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>1.8</v>
@@ -1290,58 +1290,58 @@
         <v>2.05</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q6">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="R6">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
+        <v>2.59</v>
+      </c>
+      <c r="U6">
         <v>2.88</v>
-      </c>
-      <c r="U6">
-        <v>2.9</v>
       </c>
       <c r="V6">
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC6">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="AD6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
         <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
         <v>1.9</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>3.5</v>
       </c>
       <c r="Q7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R7">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
         <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
         <v>1.66</v>
       </c>
       <c r="AB7">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC7">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AD7">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
         <v>1.56</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P8">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
         <v>3.28</v>
       </c>
       <c r="P9">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R9">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
         <v>2.53</v>
@@ -1803,25 +1803,25 @@
         <v>1.45</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC9">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
         <v>1.42</v>
@@ -1830,7 +1830,7 @@
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
         <v>2.28</v>
@@ -1849,7 +1849,7 @@
         <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,22 +1942,22 @@
         <v>1.48</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P10">
         <v>5.25</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S10">
         <v>1.27</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
         <v>2.41</v>
@@ -1981,7 +1981,7 @@
         <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
         <v>2.59</v>
@@ -1990,13 +1990,13 @@
         <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="Q11">
         <v>2.32</v>
@@ -2120,19 +2120,19 @@
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
         <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.21</v>
@@ -2141,25 +2141,25 @@
         <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
         <v>1.97</v>
       </c>
       <c r="AC11">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
         <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>4.6</v>
+        <v>3.13</v>
       </c>
       <c r="Q12">
+        <v>2.5</v>
+      </c>
+      <c r="R12">
+        <v>2.13</v>
+      </c>
+      <c r="S12">
+        <v>1.29</v>
+      </c>
+      <c r="T12">
+        <v>3.04</v>
+      </c>
+      <c r="U12">
+        <v>2.49</v>
+      </c>
+      <c r="V12">
+        <v>1.51</v>
+      </c>
+      <c r="W12">
+        <v>1.07</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.2</v>
+      </c>
+      <c r="Z12">
+        <v>4</v>
+      </c>
+      <c r="AA12">
+        <v>1.66</v>
+      </c>
+      <c r="AB12">
         <v>2.15</v>
       </c>
-      <c r="R12">
-        <v>2.15</v>
-      </c>
-      <c r="S12">
-        <v>1.33</v>
-      </c>
-      <c r="T12">
-        <v>2.88</v>
-      </c>
-      <c r="U12">
-        <v>2.56</v>
-      </c>
-      <c r="V12">
-        <v>1.41</v>
-      </c>
-      <c r="W12">
-        <v>1.06</v>
-      </c>
-      <c r="X12">
-        <v>1</v>
-      </c>
-      <c r="Y12">
-        <v>1.21</v>
-      </c>
-      <c r="Z12">
-        <v>3.58</v>
-      </c>
-      <c r="AA12">
-        <v>1.79</v>
-      </c>
-      <c r="AB12">
-        <v>1.97</v>
-      </c>
       <c r="AC12">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>3.19</v>
+        <v>2.69</v>
       </c>
       <c r="Q13">
-        <v>2.44</v>
+        <v>2.97</v>
       </c>
       <c r="R13">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
+        <v>2.79</v>
+      </c>
+      <c r="U13">
+        <v>2.67</v>
+      </c>
+      <c r="V13">
+        <v>1.38</v>
+      </c>
+      <c r="W13">
+        <v>1.05</v>
+      </c>
+      <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>3.42</v>
+      </c>
+      <c r="AA13">
+        <v>1.85</v>
+      </c>
+      <c r="AB13">
+        <v>1.91</v>
+      </c>
+      <c r="AC13">
         <v>3.04</v>
       </c>
-      <c r="U13">
-        <v>2.49</v>
-      </c>
-      <c r="V13">
-        <v>1.51</v>
-      </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>1.17</v>
-      </c>
-      <c r="Z13">
-        <v>4</v>
-      </c>
-      <c r="AA13">
-        <v>1.66</v>
-      </c>
-      <c r="AB13">
-        <v>2.15</v>
-      </c>
-      <c r="AC13">
-        <v>2.62</v>
-      </c>
       <c r="AD13">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG13">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,65 +2591,65 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P14">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q14">
+        <v>2.1</v>
+      </c>
+      <c r="R14">
+        <v>2.19</v>
+      </c>
+      <c r="S14">
+        <v>1.33</v>
+      </c>
+      <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
+        <v>2.56</v>
+      </c>
+      <c r="V14">
+        <v>1.41</v>
+      </c>
+      <c r="W14">
+        <v>1.06</v>
+      </c>
+      <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
+        <v>1.22</v>
+      </c>
+      <c r="Z14">
+        <v>3.9</v>
+      </c>
+      <c r="AA14">
+        <v>1.8</v>
+      </c>
+      <c r="AB14">
+        <v>1.94</v>
+      </c>
+      <c r="AC14">
         <v>2.81</v>
       </c>
-      <c r="R14">
-        <v>2.06</v>
-      </c>
-      <c r="S14">
-        <v>1.36</v>
-      </c>
-      <c r="T14">
-        <v>2.79</v>
-      </c>
-      <c r="U14">
-        <v>2.67</v>
-      </c>
-      <c r="V14">
-        <v>1.38</v>
-      </c>
-      <c r="W14">
-        <v>1.1</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.25</v>
-      </c>
-      <c r="Z14">
-        <v>3.42</v>
-      </c>
-      <c r="AA14">
-        <v>1.85</v>
-      </c>
-      <c r="AB14">
+      <c r="AD14">
+        <v>1.33</v>
+      </c>
+      <c r="AE14">
+        <v>1.09</v>
+      </c>
+      <c r="AF14">
+        <v>1.75</v>
+      </c>
+      <c r="AG14">
         <v>1.95</v>
       </c>
-      <c r="AC14">
-        <v>3.04</v>
-      </c>
-      <c r="AD14">
-        <v>1.29</v>
-      </c>
-      <c r="AE14">
-        <v>1.07</v>
-      </c>
-      <c r="AF14">
-        <v>1.64</v>
-      </c>
-      <c r="AG14">
-        <v>2.08</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="O16">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>4.16</v>
+        <v>3.91</v>
       </c>
       <c r="Q16">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="R16">
         <v>1.93</v>
@@ -2956,7 +2956,7 @@
         <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB16">
         <v>1.75</v>
@@ -2974,7 +2974,7 @@
         <v>1.89</v>
       </c>
       <c r="AG16">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
         <v>1.83</v>
@@ -3080,61 +3080,61 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O17">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q17">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S17">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC17">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG17">
         <v>2.23</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
         <v>3.36</v>
@@ -3282,7 +3282,7 @@
         <v>4.4</v>
       </c>
       <c r="AA18">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
         <v>2.35</v>
@@ -3300,7 +3300,7 @@
         <v>1.47</v>
       </c>
       <c r="AG18">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>5.42</v>
+        <v>3.19</v>
       </c>
       <c r="Q19">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="R19">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="S19">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U19">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V19">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3442,28 +3442,28 @@
         <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA19">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB19">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AC19">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AD19">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE19">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P20">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="S20">
         <v>1.16</v>
       </c>
       <c r="T20">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="U20">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="V20">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="W20">
         <v>1.2</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>7.5</v>
+        <v>6.32</v>
       </c>
       <c r="AA20">
+        <v>1.38</v>
+      </c>
+      <c r="AB20">
+        <v>2.97</v>
+      </c>
+      <c r="AC20">
+        <v>1.95</v>
+      </c>
+      <c r="AD20">
+        <v>1.76</v>
+      </c>
+      <c r="AE20">
         <v>1.3</v>
       </c>
-      <c r="AB20">
-        <v>3.25</v>
-      </c>
-      <c r="AC20">
-        <v>1.83</v>
-      </c>
-      <c r="AD20">
-        <v>1.87</v>
-      </c>
-      <c r="AE20">
-        <v>1.35</v>
-      </c>
       <c r="AF20">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK20">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Q21">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="R21">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T21">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
         <v>2.38</v>
       </c>
       <c r="V21">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
       <c r="AA21">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC21">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.49</v>
+        <v>2.1</v>
       </c>
       <c r="O22">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>1.56</v>
+        <v>2.75</v>
       </c>
       <c r="Q22">
-        <v>4.36</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T22">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="U22">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3931,44 +3931,44 @@
         <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5.33</v>
+        <v>4.9</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AC22">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AD22">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE22">
+        <v>1.18</v>
+      </c>
+      <c r="AF22">
+        <v>1.43</v>
+      </c>
+      <c r="AG22">
+        <v>2.5</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.22</v>
       </c>
-      <c r="AF22">
-        <v>1.47</v>
-      </c>
-      <c r="AG22">
-        <v>2.47</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>2.01</v>
-      </c>
       <c r="AK22">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>2.97</v>
+        <v>1.68</v>
       </c>
       <c r="Q23">
-        <v>2.66</v>
+        <v>4.39</v>
       </c>
       <c r="R23">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="AA23">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB23">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AC23">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD23">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE23">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>2.01</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Q24">
+        <v>2.2</v>
+      </c>
+      <c r="R24">
         <v>2.1</v>
       </c>
-      <c r="R24">
-        <v>2.08</v>
-      </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U24">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG24">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="O25">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -4399,49 +4399,49 @@
         <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="V25">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB25">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD25">
         <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG25">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="S26">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T26">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U26">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="V26">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W26">
         <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y26">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z26">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="AA26">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AB26">
         <v>1.5</v>
       </c>
       <c r="AC26">
-        <v>4.97</v>
+        <v>4.85</v>
       </c>
       <c r="AD26">
         <v>1.17</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK26">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O27">
         <v>3.5</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q27">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R27">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="U27">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
         <v>1.43</v>
@@ -4743,28 +4743,28 @@
         <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
         <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC27">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
         <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
         <v>2.02</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.61</v>
+        <v>3.1</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
+        <v>1.22</v>
+      </c>
+      <c r="Z28">
+        <v>3.8</v>
+      </c>
+      <c r="AA28">
+        <v>1.8</v>
+      </c>
+      <c r="AB28">
+        <v>2</v>
+      </c>
+      <c r="AC28">
+        <v>3</v>
+      </c>
+      <c r="AD28">
+        <v>1.3</v>
+      </c>
+      <c r="AE28">
+        <v>1.13</v>
+      </c>
+      <c r="AF28">
+        <v>1.66</v>
+      </c>
+      <c r="AG28">
+        <v>2.07</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.21</v>
+      </c>
+      <c r="AK28">
         <v>1.27</v>
-      </c>
-      <c r="Z28">
-        <v>3.15</v>
-      </c>
-      <c r="AA28">
-        <v>1.87</v>
-      </c>
-      <c r="AB28">
-        <v>1.77</v>
-      </c>
-      <c r="AC28">
-        <v>3.1</v>
-      </c>
-      <c r="AD28">
-        <v>1.28</v>
-      </c>
-      <c r="AE28">
-        <v>1.06</v>
-      </c>
-      <c r="AF28">
-        <v>1.68</v>
-      </c>
-      <c r="AG28">
-        <v>2</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.25</v>
-      </c>
-      <c r="AK28">
-        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="O29">
         <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="Q29">
-        <v>3.33</v>
+        <v>2.95</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="U29">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z29">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA29">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB29">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC29">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="AD29">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AG29">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q30">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="R30">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="AA30">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB30">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="AC30">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AD30">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AG30">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="O31">
         <v>3.25</v>
       </c>
       <c r="P31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q31">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S31">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U31">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V31">
         <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
         <v>3.42</v>
       </c>
       <c r="AA31">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC31">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
         <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK31">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="O33">
         <v>6.6</v>
       </c>
       <c r="P33">
-        <v>8.5</v>
+        <v>8.19</v>
       </c>
       <c r="Q33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R33">
         <v>3.1</v>
       </c>
       <c r="S33">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T33">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="U33">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V33">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="W33">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z33">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="AA33">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC33">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AD33">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE33">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG33">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK33">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
         <v>2.63</v>
       </c>
       <c r="R34">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.47</v>
+        <v>2.22</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AA34">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AD34">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AG34">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
         <v>3.74</v>
       </c>
       <c r="R35">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P36">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q36">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="R36">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U36">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V36">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z36">
-        <v>5.25</v>
+        <v>6.8</v>
       </c>
       <c r="AA36">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AB36">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="AC36">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="AD36">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AE36">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF36">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK36">
-        <v>2.33</v>
+        <v>2.72</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,28 +6503,28 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q38">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="R38">
         <v>2.65</v>
       </c>
       <c r="S38">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
         <v>4.6</v>
       </c>
       <c r="U38">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V38">
         <v>1.75</v>
@@ -6557,7 +6557,7 @@
         <v>1.31</v>
       </c>
       <c r="AF38">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
         <v>2.53</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="O39">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P39">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q39">
         <v>1.9</v>
       </c>
       <c r="R39">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="S39">
         <v>1.22</v>
@@ -6687,10 +6687,10 @@
         <v>3.8</v>
       </c>
       <c r="U39">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="V39">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
         <v>1.16</v>
@@ -6699,10 +6699,10 @@
         <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA39">
         <v>1.5</v>
@@ -6711,19 +6711,19 @@
         <v>2.5</v>
       </c>
       <c r="AC39">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD39">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK39">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>2.46</v>
       </c>
       <c r="Q40">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
         <v>2.11</v>
@@ -6859,31 +6859,31 @@
         <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA40">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AC40">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD40">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
         <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG40">
         <v>1.87</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O41">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q41">
-        <v>3.16</v>
+        <v>2.6</v>
       </c>
       <c r="R41">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="S41">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="U41">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V41">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB41">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AD41">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O42">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q42">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R42">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S42">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T42">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U42">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="V42">
         <v>1.56</v>
@@ -7188,7 +7188,7 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z42">
         <v>4.6</v>
@@ -7197,16 +7197,16 @@
         <v>1.57</v>
       </c>
       <c r="AB42">
+        <v>2.26</v>
+      </c>
+      <c r="AC42">
         <v>2.35</v>
       </c>
-      <c r="AC42">
-        <v>2.4</v>
-      </c>
       <c r="AD42">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF42">
         <v>1.68</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O43">
         <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA43">
         <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7487,74 +7487,74 @@
         <v>3</v>
       </c>
       <c r="P44">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="Q44">
-        <v>4.22</v>
+        <v>3.92</v>
       </c>
       <c r="R44">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T44">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="U44">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V44">
         <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
+        <v>1.3</v>
+      </c>
+      <c r="Z44">
+        <v>2.97</v>
+      </c>
+      <c r="AA44">
+        <v>2.1</v>
+      </c>
+      <c r="AB44">
+        <v>1.7</v>
+      </c>
+      <c r="AC44">
+        <v>3.5</v>
+      </c>
+      <c r="AD44">
         <v>1.22</v>
       </c>
-      <c r="Z44">
-        <v>3.14</v>
-      </c>
-      <c r="AA44">
-        <v>1.95</v>
-      </c>
-      <c r="AB44">
-        <v>1.85</v>
-      </c>
-      <c r="AC44">
-        <v>3.28</v>
-      </c>
-      <c r="AD44">
+      <c r="AE44">
+        <v>1.04</v>
+      </c>
+      <c r="AF44">
+        <v>1.62</v>
+      </c>
+      <c r="AG44">
+        <v>1.73</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.61</v>
+      </c>
+      <c r="AK44">
         <v>1.25</v>
-      </c>
-      <c r="AE44">
-        <v>1.07</v>
-      </c>
-      <c r="AF44">
-        <v>1.6</v>
-      </c>
-      <c r="AG44">
-        <v>1.75</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.24</v>
-      </c>
-      <c r="AK44">
-        <v>1.23</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,58 +1939,58 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="O10">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AD10">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="P11">
-        <v>3.87</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="R11">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>2.49</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="O14">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>4.6</v>
+        <v>3.87</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="S14">
         <v>1.33</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
         <v>1.41</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
         <v>1.8</v>
       </c>
       <c r="AB14">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AC14">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,55 +2757,55 @@
         <v>1.5</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P15">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="S15">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
         <v>2.15</v>
       </c>
       <c r="V15">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB15">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AC15">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD15">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE15">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
         <v>1.58</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P19">
-        <v>3.19</v>
+        <v>4.8</v>
       </c>
       <c r="Q19">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="R19">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="S19">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T19">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U19">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V19">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="W19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>6.1</v>
+        <v>6.32</v>
       </c>
       <c r="AA19">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AB19">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AC19">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD19">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AG19">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK19">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>3.19</v>
       </c>
       <c r="Q20">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="R20">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="S20">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T20">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U20">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V20">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>6.32</v>
+        <v>6.1</v>
       </c>
       <c r="AA20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AC20">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD20">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF20">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>4.34</v>
+        <v>1.89</v>
       </c>
       <c r="Q27">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AA27">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG27">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>1.89</v>
+        <v>4.34</v>
       </c>
       <c r="Q28">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="R28">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="U28">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
+        <v>1.93</v>
+      </c>
+      <c r="AC28">
+        <v>3.1</v>
+      </c>
+      <c r="AD28">
+        <v>1.33</v>
+      </c>
+      <c r="AE28">
+        <v>1.12</v>
+      </c>
+      <c r="AF28">
+        <v>1.75</v>
+      </c>
+      <c r="AG28">
+        <v>2.02</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.2</v>
+      </c>
+      <c r="AK28">
         <v>2</v>
-      </c>
-      <c r="AC28">
-        <v>3</v>
-      </c>
-      <c r="AD28">
-        <v>1.3</v>
-      </c>
-      <c r="AE28">
-        <v>1.13</v>
-      </c>
-      <c r="AF28">
-        <v>1.66</v>
-      </c>
-      <c r="AG28">
-        <v>2.07</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.21</v>
-      </c>
-      <c r="AK28">
-        <v>1.27</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5531,25 +5531,25 @@
         <v>3.9</v>
       </c>
       <c r="P32">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S32">
         <v>1.34</v>
       </c>
       <c r="T32">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5558,31 +5558,31 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE32">
         <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
         <v>3.2</v>
@@ -6370,7 +6370,7 @@
         <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.21</v>
@@ -6379,7 +6379,7 @@
         <v>3.6</v>
       </c>
       <c r="AA37">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
         <v>2</v>
@@ -6391,13 +6391,13 @@
         <v>1.36</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="P3">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>3.34</v>
       </c>
       <c r="R3">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.91</v>
       </c>
       <c r="V3">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>4.42</v>
+        <v>3.1</v>
       </c>
       <c r="AA3">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>2.38</v>
+        <v>1.29</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q4">
-        <v>3.34</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
+        <v>1.3</v>
+      </c>
+      <c r="T4">
+        <v>3.32</v>
+      </c>
+      <c r="U4">
+        <v>2.38</v>
+      </c>
+      <c r="V4">
+        <v>1.49</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
+        <v>1.2</v>
+      </c>
+      <c r="Z4">
+        <v>4.42</v>
+      </c>
+      <c r="AA4">
+        <v>1.66</v>
+      </c>
+      <c r="AB4">
+        <v>2.15</v>
+      </c>
+      <c r="AC4">
+        <v>2.52</v>
+      </c>
+      <c r="AD4">
         <v>1.41</v>
       </c>
-      <c r="T4">
-        <v>2.75</v>
-      </c>
-      <c r="U4">
-        <v>2.91</v>
-      </c>
-      <c r="V4">
-        <v>1.33</v>
-      </c>
-      <c r="W4">
-        <v>1.04</v>
-      </c>
-      <c r="X4">
-        <v>1.06</v>
-      </c>
-      <c r="Y4">
-        <v>1.33</v>
-      </c>
-      <c r="Z4">
-        <v>3.1</v>
-      </c>
-      <c r="AA4">
+      <c r="AE4">
+        <v>1.14</v>
+      </c>
+      <c r="AF4">
+        <v>1.67</v>
+      </c>
+      <c r="AG4">
         <v>2.1</v>
       </c>
-      <c r="AB4">
-        <v>1.65</v>
-      </c>
-      <c r="AC4">
-        <v>3.8</v>
-      </c>
-      <c r="AD4">
-        <v>1.25</v>
-      </c>
-      <c r="AE4">
-        <v>1.07</v>
-      </c>
-      <c r="AF4">
-        <v>1.8</v>
-      </c>
-      <c r="AG4">
-        <v>1.81</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK4">
-        <v>1.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="O11">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>5.25</v>
+        <v>3.13</v>
       </c>
       <c r="Q11">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S11">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U11">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W11">
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB11">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>2.49</v>
+        <v>1.63</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.13</v>
+        <v>2.69</v>
       </c>
       <c r="Q12">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="R12">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
+        <v>2.79</v>
+      </c>
+      <c r="U12">
+        <v>2.67</v>
+      </c>
+      <c r="V12">
+        <v>1.38</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1.04</v>
+      </c>
+      <c r="Y12">
+        <v>1.25</v>
+      </c>
+      <c r="Z12">
+        <v>3.42</v>
+      </c>
+      <c r="AA12">
+        <v>1.85</v>
+      </c>
+      <c r="AB12">
+        <v>1.91</v>
+      </c>
+      <c r="AC12">
         <v>3.04</v>
       </c>
-      <c r="U12">
-        <v>2.49</v>
-      </c>
-      <c r="V12">
-        <v>1.51</v>
-      </c>
-      <c r="W12">
+      <c r="AD12">
+        <v>1.33</v>
+      </c>
+      <c r="AE12">
         <v>1.07</v>
       </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>1.2</v>
-      </c>
-      <c r="Z12">
-        <v>4</v>
-      </c>
-      <c r="AA12">
-        <v>1.66</v>
-      </c>
-      <c r="AB12">
-        <v>2.15</v>
-      </c>
-      <c r="AC12">
-        <v>2.62</v>
-      </c>
-      <c r="AD12">
-        <v>1.38</v>
-      </c>
-      <c r="AE12">
-        <v>1.11</v>
-      </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG12">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P13">
-        <v>2.69</v>
+        <v>5.25</v>
       </c>
       <c r="Q13">
-        <v>2.97</v>
+        <v>1.91</v>
       </c>
       <c r="R13">
+        <v>2.4</v>
+      </c>
+      <c r="S13">
+        <v>1.27</v>
+      </c>
+      <c r="T13">
+        <v>3.25</v>
+      </c>
+      <c r="U13">
+        <v>2.41</v>
+      </c>
+      <c r="V13">
+        <v>1.46</v>
+      </c>
+      <c r="W13">
+        <v>1.07</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.16</v>
+      </c>
+      <c r="Z13">
+        <v>4.1</v>
+      </c>
+      <c r="AA13">
+        <v>1.65</v>
+      </c>
+      <c r="AB13">
         <v>2.07</v>
       </c>
-      <c r="S13">
-        <v>1.35</v>
-      </c>
-      <c r="T13">
-        <v>2.79</v>
-      </c>
-      <c r="U13">
-        <v>2.67</v>
-      </c>
-      <c r="V13">
-        <v>1.38</v>
-      </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.42</v>
-      </c>
-      <c r="AA13">
-        <v>1.85</v>
-      </c>
-      <c r="AB13">
-        <v>1.91</v>
-      </c>
       <c r="AC13">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.44</v>
+        <v>2.49</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>4.8</v>
+        <v>3.19</v>
       </c>
       <c r="Q19">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="R19">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="S19">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U19">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V19">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>6.32</v>
+        <v>6.1</v>
       </c>
       <c r="AA19">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB19">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AC19">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD19">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE19">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P20">
-        <v>3.19</v>
+        <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="S20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U20">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V20">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>6.1</v>
+        <v>6.32</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AB20">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AC20">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD20">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK20">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q29">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="R29">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T29">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="V29">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z29">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="AA29">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB29">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="AD29">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AG29">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q30">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="R30">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="U30">
-        <v>2.78</v>
+        <v>2.51</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="AA30">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -644,19 +644,19 @@
         <v>3.25</v>
       </c>
       <c r="Q2">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R2">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
         <v>1.46</v>
@@ -668,16 +668,16 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA2">
         <v>1.7</v>
       </c>
       <c r="AB2">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AC2">
         <v>2.75</v>
@@ -686,17 +686,17 @@
         <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "47", "48", "77"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -708,34 +708,34 @@
         <v>1.19</v>
       </c>
       <c r="AK2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -787,21 +787,21 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
         <v>2.2</v>
@@ -810,16 +810,16 @@
         <v>3.34</v>
       </c>
       <c r="R3">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
         <v>1.41</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U3">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -831,25 +831,25 @@
         <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA3">
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD3">
         <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
         <v>1.8</v>
@@ -859,46 +859,46 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,39 +938,39 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
         <v>1.5</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P4">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
         <v>2.4</v>
@@ -982,28 +982,28 @@
         <v>3.32</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
         <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB4">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
         <v>2.52</v>
@@ -1012,56 +1012,56 @@
         <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
         <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "56", "63", "73"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "85", "90+2"]</t>
         </is>
       </c>
       <c r="AJ4">
         <v>1.08</v>
       </c>
       <c r="AK4">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>4.6</v>
+        <v>2.69</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="R10">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U10">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC10">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AD10">
         <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P12">
-        <v>2.69</v>
+        <v>5.25</v>
       </c>
       <c r="Q12">
-        <v>2.97</v>
+        <v>1.91</v>
       </c>
       <c r="R12">
+        <v>2.4</v>
+      </c>
+      <c r="S12">
+        <v>1.27</v>
+      </c>
+      <c r="T12">
+        <v>3.25</v>
+      </c>
+      <c r="U12">
+        <v>2.41</v>
+      </c>
+      <c r="V12">
+        <v>1.46</v>
+      </c>
+      <c r="W12">
+        <v>1.07</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.16</v>
+      </c>
+      <c r="Z12">
+        <v>4.1</v>
+      </c>
+      <c r="AA12">
+        <v>1.65</v>
+      </c>
+      <c r="AB12">
         <v>2.07</v>
       </c>
-      <c r="S12">
-        <v>1.35</v>
-      </c>
-      <c r="T12">
-        <v>2.79</v>
-      </c>
-      <c r="U12">
-        <v>2.67</v>
-      </c>
-      <c r="V12">
-        <v>1.38</v>
-      </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.25</v>
-      </c>
-      <c r="Z12">
-        <v>3.42</v>
-      </c>
-      <c r="AA12">
-        <v>1.85</v>
-      </c>
-      <c r="AB12">
-        <v>1.91</v>
-      </c>
       <c r="AC12">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE12">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>1.44</v>
+        <v>2.49</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,58 +2428,58 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="O13">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q13">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S13">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA13">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB13">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC13">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AD13">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="P22">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q22">
+        <v>4.39</v>
+      </c>
+      <c r="R22">
         <v>2.5</v>
       </c>
-      <c r="R22">
-        <v>2.22</v>
-      </c>
       <c r="S22">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="V22">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB22">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AC22">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD22">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE22">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>2.01</v>
       </c>
       <c r="AK22">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
-        <v>4.39</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
+        <v>2.22</v>
+      </c>
+      <c r="S23">
+        <v>1.24</v>
+      </c>
+      <c r="T23">
+        <v>3.34</v>
+      </c>
+      <c r="U23">
+        <v>2.24</v>
+      </c>
+      <c r="V23">
+        <v>1.57</v>
+      </c>
+      <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
+        <v>1.01</v>
+      </c>
+      <c r="Y23">
+        <v>1.11</v>
+      </c>
+      <c r="Z23">
+        <v>4.9</v>
+      </c>
+      <c r="AA23">
+        <v>1.53</v>
+      </c>
+      <c r="AB23">
+        <v>2.43</v>
+      </c>
+      <c r="AC23">
+        <v>2.27</v>
+      </c>
+      <c r="AD23">
+        <v>1.6</v>
+      </c>
+      <c r="AE23">
+        <v>1.18</v>
+      </c>
+      <c r="AF23">
+        <v>1.43</v>
+      </c>
+      <c r="AG23">
         <v>2.5</v>
       </c>
-      <c r="S23">
-        <v>1.2</v>
-      </c>
-      <c r="T23">
-        <v>4</v>
-      </c>
-      <c r="U23">
-        <v>2</v>
-      </c>
-      <c r="V23">
-        <v>1.73</v>
-      </c>
-      <c r="W23">
-        <v>1.13</v>
-      </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.15</v>
-      </c>
-      <c r="Z23">
-        <v>5.15</v>
-      </c>
-      <c r="AA23">
-        <v>1.43</v>
-      </c>
-      <c r="AB23">
-        <v>2.6</v>
-      </c>
-      <c r="AC23">
-        <v>2.26</v>
-      </c>
-      <c r="AD23">
-        <v>1.62</v>
-      </c>
-      <c r="AE23">
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.22</v>
       </c>
-      <c r="AF23">
-        <v>1.44</v>
-      </c>
-      <c r="AG23">
-        <v>2.55</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>2.01</v>
-      </c>
       <c r="AK23">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.66</v>
+        <v>2.58</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.34</v>
+        <v>2.27</v>
       </c>
       <c r="Q28">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AG28">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="O29">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.4</v>
+        <v>4.34</v>
       </c>
       <c r="Q29">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="R29">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="U29">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AC29">
         <v>3.1</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF29">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
+        <v>2.02</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.2</v>
+      </c>
+      <c r="AK29">
         <v>2</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.25</v>
-      </c>
-      <c r="AK29">
-        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q30">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="R30">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="V30">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="AA30">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC30">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="AD30">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AG30">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.38</v>
+        <v>2.49</v>
       </c>
       <c r="O39">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="P39">
-        <v>4.6</v>
+        <v>2.46</v>
       </c>
       <c r="Q39">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="U39">
-        <v>2.01</v>
+        <v>2.63</v>
       </c>
       <c r="V39">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W39">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="AC39">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.49</v>
+        <v>1.38</v>
       </c>
       <c r="O40">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="P40">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="R40">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="U40">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="V40">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y40">
+        <v>1.08</v>
+      </c>
+      <c r="Z40">
+        <v>5.1</v>
+      </c>
+      <c r="AA40">
+        <v>1.5</v>
+      </c>
+      <c r="AB40">
+        <v>2.5</v>
+      </c>
+      <c r="AC40">
+        <v>2.15</v>
+      </c>
+      <c r="AD40">
+        <v>1.57</v>
+      </c>
+      <c r="AE40">
         <v>1.25</v>
       </c>
-      <c r="Z40">
-        <v>2.75</v>
-      </c>
-      <c r="AA40">
-        <v>1.85</v>
-      </c>
-      <c r="AB40">
-        <v>1.69</v>
-      </c>
-      <c r="AC40">
-        <v>3</v>
-      </c>
-      <c r="AD40">
-        <v>1.25</v>
-      </c>
-      <c r="AE40">
-        <v>1.09</v>
-      </c>
       <c r="AF40">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1101,130 +1101,130 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="O5">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>3.59</v>
+        <v>4.3</v>
       </c>
       <c r="Q5">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="R5">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA5">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
         <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "27", "36", "40", "58"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="Q6">
         <v>2.55</v>
@@ -1302,28 +1302,28 @@
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
         <v>1.95</v>
@@ -1332,7 +1332,7 @@
         <v>1.73</v>
       </c>
       <c r="AC6">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="AD6">
         <v>1.25</v>
@@ -1341,7 +1341,7 @@
         <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
         <v>1.9</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="Q7">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R7">
         <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1486,28 +1486,28 @@
         <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>4.51</v>
       </c>
       <c r="AA7">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
+        <v>3.3</v>
+      </c>
+      <c r="P8">
+        <v>2.37</v>
+      </c>
+      <c r="Q8">
         <v>3.05</v>
       </c>
-      <c r="P8">
-        <v>2.85</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.3</v>
@@ -1797,28 +1797,28 @@
         <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC9">
         <v>2.8</v>
@@ -1827,13 +1827,13 @@
         <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
         <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK9">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,16 +1907,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,118 +1928,118 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>1.29</v>
+      </c>
+      <c r="T10">
+        <v>3.04</v>
+      </c>
+      <c r="U10">
+        <v>2.5</v>
+      </c>
+      <c r="V10">
+        <v>1.52</v>
+      </c>
+      <c r="W10">
+        <v>1.07</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.21</v>
+      </c>
+      <c r="Z10">
+        <v>4.4</v>
+      </c>
+      <c r="AA10">
+        <v>1.66</v>
+      </c>
+      <c r="AB10">
         <v>2.07</v>
       </c>
-      <c r="S10">
-        <v>1.35</v>
-      </c>
-      <c r="T10">
-        <v>2.79</v>
-      </c>
-      <c r="U10">
-        <v>2.67</v>
-      </c>
-      <c r="V10">
-        <v>1.38</v>
-      </c>
-      <c r="W10">
-        <v>1.05</v>
-      </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>1.25</v>
-      </c>
-      <c r="Z10">
-        <v>3.42</v>
-      </c>
-      <c r="AA10">
-        <v>1.85</v>
-      </c>
-      <c r="AB10">
-        <v>1.91</v>
-      </c>
       <c r="AC10">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
+          <t>["89"]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2070,139 +2070,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="O11">
         <v>3.5</v>
       </c>
       <c r="P11">
-        <v>3.13</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="R11">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
         <v>3.04</v>
       </c>
       <c r="U11">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.25</v>
+      </c>
+      <c r="Z11">
+        <v>3.7</v>
+      </c>
+      <c r="AA11">
+        <v>1.85</v>
+      </c>
+      <c r="AB11">
+        <v>1.9</v>
+      </c>
+      <c r="AC11">
+        <v>2.97</v>
+      </c>
+      <c r="AD11">
+        <v>1.3</v>
+      </c>
+      <c r="AE11">
+        <v>1.08</v>
+      </c>
+      <c r="AF11">
+        <v>1.78</v>
+      </c>
+      <c r="AG11">
+        <v>1.95</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>["43", "89"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>["24"]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.18</v>
+      </c>
+      <c r="AK11">
+        <v>2.1</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>6</v>
+      </c>
+      <c r="AN11">
+        <v>4</v>
+      </c>
+      <c r="AO11">
+        <v>14</v>
+      </c>
+      <c r="AP11">
+        <v>9</v>
+      </c>
+      <c r="AQ11">
+        <v>1.58</v>
+      </c>
+      <c r="AR11">
         <v>1.07</v>
       </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.2</v>
-      </c>
-      <c r="Z11">
-        <v>4</v>
-      </c>
-      <c r="AA11">
-        <v>1.66</v>
-      </c>
-      <c r="AB11">
-        <v>2.15</v>
-      </c>
-      <c r="AC11">
-        <v>2.62</v>
-      </c>
-      <c r="AD11">
-        <v>1.38</v>
-      </c>
-      <c r="AE11">
-        <v>1.11</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
-      <c r="AG11">
-        <v>2.24</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.23</v>
-      </c>
-      <c r="AK11">
-        <v>1.63</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>-1</v>
-      </c>
-      <c r="AN11">
-        <v>-1</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>-1</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
       <c r="AS11">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2254,118 +2254,118 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O12">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P12">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
+        <v>1.18</v>
+      </c>
+      <c r="Z12">
+        <v>3.88</v>
+      </c>
+      <c r="AA12">
+        <v>1.7</v>
+      </c>
+      <c r="AB12">
+        <v>1.98</v>
+      </c>
+      <c r="AC12">
+        <v>2.74</v>
+      </c>
+      <c r="AD12">
+        <v>1.35</v>
+      </c>
+      <c r="AE12">
+        <v>1.1</v>
+      </c>
+      <c r="AF12">
+        <v>1.78</v>
+      </c>
+      <c r="AG12">
+        <v>1.93</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>["67", "85"]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.16</v>
       </c>
-      <c r="Z12">
-        <v>4.1</v>
-      </c>
-      <c r="AA12">
-        <v>1.65</v>
-      </c>
-      <c r="AB12">
-        <v>2.07</v>
-      </c>
-      <c r="AC12">
-        <v>2.59</v>
-      </c>
-      <c r="AD12">
-        <v>1.39</v>
-      </c>
-      <c r="AE12">
-        <v>1.13</v>
-      </c>
-      <c r="AF12">
-        <v>1.75</v>
-      </c>
-      <c r="AG12">
-        <v>1.95</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.14</v>
-      </c>
       <c r="AK12">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2417,118 +2417,118 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q13">
+        <v>2.4</v>
+      </c>
+      <c r="R13">
         <v>2.1</v>
       </c>
-      <c r="R13">
-        <v>2.19</v>
-      </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>4</v>
+      </c>
+      <c r="AA13">
+        <v>1.85</v>
+      </c>
+      <c r="AB13">
+        <v>1.91</v>
+      </c>
+      <c r="AC13">
+        <v>3.1</v>
+      </c>
+      <c r="AD13">
+        <v>1.36</v>
+      </c>
+      <c r="AE13">
+        <v>1.11</v>
+      </c>
+      <c r="AF13">
+        <v>1.67</v>
+      </c>
+      <c r="AG13">
+        <v>2.05</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>["87"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>["90+4"]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.22</v>
       </c>
-      <c r="Z13">
-        <v>3.9</v>
-      </c>
-      <c r="AA13">
-        <v>1.8</v>
-      </c>
-      <c r="AB13">
-        <v>1.94</v>
-      </c>
-      <c r="AC13">
-        <v>2.81</v>
-      </c>
-      <c r="AD13">
-        <v>1.33</v>
-      </c>
-      <c r="AE13">
-        <v>1.09</v>
-      </c>
-      <c r="AF13">
-        <v>1.75</v>
-      </c>
-      <c r="AG13">
-        <v>1.95</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.17</v>
-      </c>
       <c r="AK13">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14">
@@ -2587,68 +2587,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>3.87</v>
+        <v>2.69</v>
       </c>
       <c r="Q14">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="R14">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA14">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD14">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,37 +2661,37 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="O16">
+        <v>3.2</v>
+      </c>
+      <c r="P16">
         <v>3.25</v>
       </c>
-      <c r="P16">
-        <v>3.91</v>
-      </c>
       <c r="Q16">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="R16">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="S16">
         <v>1.51</v>
@@ -2956,25 +2956,25 @@
         <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC16">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
         <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG16">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="O17">
         <v>3.5</v>
       </c>
       <c r="P17">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q17">
+        <v>2.2</v>
+      </c>
+      <c r="R17">
+        <v>2.5</v>
+      </c>
+      <c r="S17">
+        <v>1.25</v>
+      </c>
+      <c r="T17">
+        <v>3.42</v>
+      </c>
+      <c r="U17">
+        <v>2.21</v>
+      </c>
+      <c r="V17">
+        <v>1.67</v>
+      </c>
+      <c r="W17">
+        <v>1.12</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.11</v>
+      </c>
+      <c r="Z17">
+        <v>5.4</v>
+      </c>
+      <c r="AA17">
+        <v>1.48</v>
+      </c>
+      <c r="AB17">
+        <v>2.7</v>
+      </c>
+      <c r="AC17">
+        <v>2.25</v>
+      </c>
+      <c r="AD17">
+        <v>1.61</v>
+      </c>
+      <c r="AE17">
+        <v>1.2</v>
+      </c>
+      <c r="AF17">
+        <v>1.44</v>
+      </c>
+      <c r="AG17">
         <v>2.38</v>
       </c>
-      <c r="R17">
-        <v>2.35</v>
-      </c>
-      <c r="S17">
-        <v>1.29</v>
-      </c>
-      <c r="T17">
-        <v>3.25</v>
-      </c>
-      <c r="U17">
-        <v>2.45</v>
-      </c>
-      <c r="V17">
-        <v>1.49</v>
-      </c>
-      <c r="W17">
-        <v>1.1</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>1.2</v>
-      </c>
-      <c r="Z17">
-        <v>4.5</v>
-      </c>
-      <c r="AA17">
-        <v>1.63</v>
-      </c>
-      <c r="AB17">
-        <v>2.17</v>
-      </c>
-      <c r="AC17">
-        <v>2.6</v>
-      </c>
-      <c r="AD17">
-        <v>1.45</v>
-      </c>
-      <c r="AE17">
-        <v>1.16</v>
-      </c>
-      <c r="AF17">
-        <v>1.56</v>
-      </c>
-      <c r="AG17">
-        <v>2.23</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
         <v>3.36</v>
@@ -3258,7 +3258,7 @@
         <v>2.27</v>
       </c>
       <c r="S18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
         <v>3.2</v>
@@ -3276,16 +3276,16 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
         <v>4.4</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
         <v>2.33</v>
@@ -3297,7 +3297,7 @@
         <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
         <v>2.42</v>
@@ -3409,31 +3409,31 @@
         <v>1.75</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="Q19">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="R19">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="S19">
         <v>1.18</v>
       </c>
       <c r="T19">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="U19">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V19">
         <v>1.84</v>
       </c>
       <c r="W19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3442,25 +3442,25 @@
         <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
+        <v>1.36</v>
+      </c>
+      <c r="AB19">
+        <v>2.88</v>
+      </c>
+      <c r="AC19">
+        <v>1.87</v>
+      </c>
+      <c r="AD19">
+        <v>1.83</v>
+      </c>
+      <c r="AE19">
         <v>1.33</v>
       </c>
-      <c r="AB19">
-        <v>3.25</v>
-      </c>
-      <c r="AC19">
-        <v>1.85</v>
-      </c>
-      <c r="AD19">
-        <v>1.85</v>
-      </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>1.36</v>
-      </c>
-      <c r="AF19">
-        <v>1.33</v>
       </c>
       <c r="AG19">
         <v>3</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O20">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q20">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="R20">
         <v>2.62</v>
@@ -3593,7 +3593,7 @@
         <v>1.99</v>
       </c>
       <c r="V20">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W20">
         <v>1.2</v>
@@ -3605,28 +3605,28 @@
         <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>6.32</v>
+        <v>6.51</v>
       </c>
       <c r="AA20">
         <v>1.38</v>
       </c>
       <c r="AB20">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AC20">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD20">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE20">
         <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O21">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="Q21">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="R21">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U21">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="AA21">
         <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>2.69</v>
+        <v>2.46</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="O22">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>1.68</v>
+        <v>2.95</v>
       </c>
       <c r="Q22">
-        <v>4.39</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
+        <v>2.22</v>
+      </c>
+      <c r="S22">
+        <v>1.24</v>
+      </c>
+      <c r="T22">
+        <v>3.34</v>
+      </c>
+      <c r="U22">
+        <v>2.27</v>
+      </c>
+      <c r="V22">
+        <v>1.63</v>
+      </c>
+      <c r="W22">
+        <v>1.1</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.16</v>
+      </c>
+      <c r="Z22">
+        <v>5.19</v>
+      </c>
+      <c r="AA22">
+        <v>1.53</v>
+      </c>
+      <c r="AB22">
+        <v>2.37</v>
+      </c>
+      <c r="AC22">
+        <v>2.27</v>
+      </c>
+      <c r="AD22">
+        <v>1.56</v>
+      </c>
+      <c r="AE22">
+        <v>1.18</v>
+      </c>
+      <c r="AF22">
+        <v>1.43</v>
+      </c>
+      <c r="AG22">
         <v>2.5</v>
       </c>
-      <c r="S22">
-        <v>1.2</v>
-      </c>
-      <c r="T22">
-        <v>4</v>
-      </c>
-      <c r="U22">
-        <v>2</v>
-      </c>
-      <c r="V22">
-        <v>1.73</v>
-      </c>
-      <c r="W22">
-        <v>1.13</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.15</v>
-      </c>
-      <c r="Z22">
-        <v>5.15</v>
-      </c>
-      <c r="AA22">
-        <v>1.43</v>
-      </c>
-      <c r="AB22">
-        <v>2.6</v>
-      </c>
-      <c r="AC22">
-        <v>2.26</v>
-      </c>
-      <c r="AD22">
-        <v>1.62</v>
-      </c>
-      <c r="AE22">
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.22</v>
       </c>
-      <c r="AF22">
-        <v>1.44</v>
-      </c>
-      <c r="AG22">
-        <v>2.55</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>2.01</v>
-      </c>
       <c r="AK22">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
+        <v>3.3</v>
+      </c>
+      <c r="O23">
+        <v>3.8</v>
+      </c>
+      <c r="P23">
+        <v>1.71</v>
+      </c>
+      <c r="Q23">
+        <v>3.85</v>
+      </c>
+      <c r="R23">
+        <v>2.5</v>
+      </c>
+      <c r="S23">
+        <v>1.2</v>
+      </c>
+      <c r="T23">
+        <v>3.7</v>
+      </c>
+      <c r="U23">
         <v>2.1</v>
       </c>
-      <c r="O23">
-        <v>3.5</v>
-      </c>
-      <c r="P23">
-        <v>2.75</v>
-      </c>
-      <c r="Q23">
-        <v>2.5</v>
-      </c>
-      <c r="R23">
-        <v>2.22</v>
-      </c>
-      <c r="S23">
-        <v>1.24</v>
-      </c>
-      <c r="T23">
-        <v>3.34</v>
-      </c>
-      <c r="U23">
-        <v>2.24</v>
-      </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB23">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AC23">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AD23">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE23">
+        <v>1.22</v>
+      </c>
+      <c r="AF23">
+        <v>1.44</v>
+      </c>
+      <c r="AG23">
+        <v>2.55</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.18</v>
       </c>
-      <c r="AF23">
-        <v>1.43</v>
-      </c>
-      <c r="AG23">
-        <v>2.5</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
+      <c r="AK23">
         <v>1.22</v>
-      </c>
-      <c r="AK23">
-        <v>1.58</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,61 +4224,61 @@
         <v>1.63</v>
       </c>
       <c r="O24">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P24">
         <v>5.3</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R24">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T24">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="U24">
         <v>2.88</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
         <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA24">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,16 +4387,16 @@
         <v>2.7</v>
       </c>
       <c r="O25">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P25">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q25">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.36</v>
@@ -4405,43 +4405,43 @@
         <v>2.8</v>
       </c>
       <c r="U25">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z25">
+        <v>3.14</v>
+      </c>
+      <c r="AA25">
+        <v>2</v>
+      </c>
+      <c r="AB25">
+        <v>1.8</v>
+      </c>
+      <c r="AC25">
         <v>3.5</v>
       </c>
-      <c r="AA25">
-        <v>2.1</v>
-      </c>
-      <c r="AB25">
-        <v>1.87</v>
-      </c>
-      <c r="AC25">
-        <v>3.4</v>
-      </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG25">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O26">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P26">
         <v>3.4</v>
@@ -4562,49 +4562,49 @@
         <v>2.01</v>
       </c>
       <c r="S26">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="T26">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U26">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="V26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
         <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y26">
         <v>1.5</v>
       </c>
       <c r="Z26">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AA26">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AB26">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC26">
         <v>4.85</v>
       </c>
       <c r="AD26">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
         <v>2.14</v>
       </c>
       <c r="AG26">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q27">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
         <v>2.18</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U27">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.03</v>
@@ -4746,7 +4746,7 @@
         <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA27">
         <v>1.8</v>
@@ -4758,16 +4758,16 @@
         <v>3</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R28">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U28">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="V28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB28">
         <v>2.1</v>
       </c>
       <c r="AC28">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD28">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
         <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4.34</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="U29">
         <v>2.75</v>
@@ -5066,34 +5066,34 @@
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB29">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC29">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE29">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG29">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
         <v>2</v>
@@ -5199,43 +5199,43 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="R30">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U30">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AA30">
         <v>1.87</v>
@@ -5250,13 +5250,13 @@
         <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF30">
         <v>1.68</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P31">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q31">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="R31">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S31">
         <v>1.38</v>
@@ -5398,19 +5398,19 @@
         <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD31">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
         <v>1.07</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5691,31 +5691,31 @@
         <v>1.24</v>
       </c>
       <c r="O33">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="P33">
-        <v>8.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q33">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R33">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="S33">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T33">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="U33">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V33">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="W33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5727,25 +5727,25 @@
         <v>8.5</v>
       </c>
       <c r="AA33">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AB33">
         <v>3.4</v>
       </c>
       <c r="AC33">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AD33">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AE33">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AF33">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
         <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q34">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="R34">
         <v>2.23</v>
@@ -5872,16 +5872,16 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.18</v>
@@ -5890,25 +5890,25 @@
         <v>4.65</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AC34">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
         <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG34">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6023,10 +6023,10 @@
         <v>2.2</v>
       </c>
       <c r="Q35">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6050,10 +6050,10 @@
         <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA35">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB35">
         <v>1.8</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK35">
         <v>1.31</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="O36">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P36">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q36">
         <v>1.77</v>
       </c>
       <c r="R36">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U36">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V36">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z36">
-        <v>6.8</v>
+        <v>6.05</v>
       </c>
       <c r="AA36">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB36">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AC36">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD36">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AE36">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AF36">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK36">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>4.8</v>
       </c>
       <c r="R38">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="S38">
         <v>1.2</v>
@@ -6527,7 +6527,7 @@
         <v>2</v>
       </c>
       <c r="V38">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W38">
         <v>1.21</v>
@@ -6539,7 +6539,7 @@
         <v>1.07</v>
       </c>
       <c r="Z38">
-        <v>5.9</v>
+        <v>6.41</v>
       </c>
       <c r="AA38">
         <v>1.33</v>
@@ -6548,16 +6548,16 @@
         <v>2.83</v>
       </c>
       <c r="AC38">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AD38">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE38">
         <v>1.31</v>
       </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG38">
         <v>2.53</v>
@@ -6576,7 +6576,7 @@
         <v>1.12</v>
       </c>
       <c r="AK38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="O39">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P39">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="U39">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V39">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6702,25 +6702,25 @@
         <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA39">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB39">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AG39">
         <v>1.87</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AK39">
         <v>1.36</v>
@@ -6838,34 +6838,34 @@
         <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R40">
         <v>2.55</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U40">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA40">
         <v>1.5</v>
@@ -6874,7 +6874,7 @@
         <v>2.5</v>
       </c>
       <c r="AC40">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD40">
         <v>1.57</v>
@@ -6883,10 +6883,10 @@
         <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6998,19 +6998,19 @@
         <v>3.3</v>
       </c>
       <c r="P41">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
       </c>
       <c r="R41">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U41">
         <v>2.62</v>
@@ -7022,34 +7022,34 @@
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA41">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
         <v>3</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE41">
         <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
         <v>1.63</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O42">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P42">
-        <v>5.7</v>
+        <v>5.78</v>
       </c>
       <c r="Q42">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R42">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S42">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T42">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="V42">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA42">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB42">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AC42">
         <v>2.35</v>
       </c>
       <c r="AD42">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE42">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF42">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q43">
-        <v>3.54</v>
+        <v>3.96</v>
       </c>
       <c r="R43">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="U43">
         <v>2.56</v>
@@ -7348,19 +7348,19 @@
         <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC43">
         <v>2.83</v>
@@ -7369,13 +7369,13 @@
         <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG43">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK43">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="Q44">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="R44">
         <v>2.2</v>
       </c>
       <c r="S44">
+        <v>1.28</v>
+      </c>
+      <c r="T44">
+        <v>3.02</v>
+      </c>
+      <c r="U44">
+        <v>2.53</v>
+      </c>
+      <c r="V44">
         <v>1.38</v>
       </c>
-      <c r="T44">
-        <v>2.67</v>
-      </c>
-      <c r="U44">
+      <c r="W44">
+        <v>1.09</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.21</v>
+      </c>
+      <c r="Z44">
+        <v>3.58</v>
+      </c>
+      <c r="AA44">
+        <v>1.8</v>
+      </c>
+      <c r="AB44">
+        <v>2</v>
+      </c>
+      <c r="AC44">
         <v>2.88</v>
       </c>
-      <c r="V44">
-        <v>1.36</v>
-      </c>
-      <c r="W44">
-        <v>1.07</v>
-      </c>
-      <c r="X44">
-        <v>1.03</v>
-      </c>
-      <c r="Y44">
-        <v>1.3</v>
-      </c>
-      <c r="Z44">
-        <v>2.97</v>
-      </c>
-      <c r="AA44">
-        <v>2.1</v>
-      </c>
-      <c r="AB44">
-        <v>1.7</v>
-      </c>
-      <c r="AC44">
-        <v>3.5</v>
-      </c>
       <c r="AD44">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE44">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="AK44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-07-24.xlsx
+++ b/jogos_2026-07-24.xlsx
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73", "90+4"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "45+3"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "28", "65", "90"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "55", "90+2"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "23"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "49"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -2731,57 +2731,57 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
         <v>1.5</v>
       </c>
       <c r="O15">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P15">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q15">
         <v>2.02</v>
       </c>
       <c r="R15">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,19 +2793,19 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB15">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AC15">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AD15">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
         <v>1.58</v>
@@ -2815,46 +2815,46 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
+          <t>["13", "59"]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "36"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -3069,14 +3069,14 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,139 +3211,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.65</v>
+        <v>1.47</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P18">
-        <v>2.25</v>
+        <v>5.25</v>
       </c>
       <c r="Q18">
-        <v>3.36</v>
+        <v>1.84</v>
       </c>
       <c r="R18">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="V18">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
+        <v>1.11</v>
+      </c>
+      <c r="Z18">
+        <v>6.51</v>
+      </c>
+      <c r="AA18">
+        <v>1.38</v>
+      </c>
+      <c r="AB18">
+        <v>3.02</v>
+      </c>
+      <c r="AC18">
+        <v>1.93</v>
+      </c>
+      <c r="AD18">
+        <v>1.77</v>
+      </c>
+      <c r="AE18">
+        <v>1.3</v>
+      </c>
+      <c r="AF18">
+        <v>1.47</v>
+      </c>
+      <c r="AG18">
+        <v>2.45</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>["24", "77"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.15</v>
       </c>
-      <c r="Z18">
-        <v>4.4</v>
-      </c>
-      <c r="AA18">
-        <v>1.6</v>
-      </c>
-      <c r="AB18">
-        <v>2.3</v>
-      </c>
-      <c r="AC18">
-        <v>2.33</v>
-      </c>
-      <c r="AD18">
-        <v>1.48</v>
-      </c>
-      <c r="AE18">
-        <v>1.17</v>
-      </c>
-      <c r="AF18">
-        <v>1.45</v>
-      </c>
-      <c r="AG18">
-        <v>2.42</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.22</v>
-      </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>2.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,26 +3383,26 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "16", "45+1"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "64"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,139 +3537,139 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>1.47</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>5.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>1.84</v>
+        <v>3.36</v>
       </c>
       <c r="R20">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="S20">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>6.51</v>
+        <v>4.4</v>
       </c>
       <c r="AA20">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC20">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AD20">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AE20">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF20">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG20">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "12", "81", "84"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "14", "40", "52", "79"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "86"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3884,14 +3884,14 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "87"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "78"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4047,14 +4047,14 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "67", "78"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,26 +4687,26 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "59", "86", "86", "90+5", "90+5"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,26 +4850,26 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "80"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,16 +5013,16 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "29"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "54"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O32">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R32">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>4.27</v>
+        <v>5.09</v>
       </c>
       <c r="AA32">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AD32">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AE32">
         <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q37">
         <v>2.5</v>
@@ -6355,49 +6355,49 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
         <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC37">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
